--- a/dq_flux.xlsx
+++ b/dq_flux.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.업무폴더\2026년도업무\5.전략연구사업\IONIQ5_FEMM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barts\femm_ioniq5\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -690,7 +690,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -834,71 +834,76 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$L$2:$L$20</c:f>
+              <c:f>Lambda_d_matrix!$C$2:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>108.63</c:v>
+                  <c:v>135.63</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98.22</c:v>
+                  <c:v>134.13</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.14</c:v>
+                  <c:v>132.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>75.97</c:v>
+                  <c:v>131.19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.09</c:v>
+                  <c:v>129.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>54.55</c:v>
+                  <c:v>128.37</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44.32</c:v>
+                  <c:v>127.04</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>34.409999999999997</c:v>
+                  <c:v>125.78</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.78</c:v>
+                  <c:v>124.58</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.5</c:v>
+                  <c:v>123.48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.55</c:v>
+                  <c:v>122.46</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.61</c:v>
+                  <c:v>121.54</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-11.97</c:v>
+                  <c:v>120.73</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-20.23</c:v>
+                  <c:v>120.03</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-27.3</c:v>
+                  <c:v>119.46</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-33.11</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-37.18</c:v>
+                  <c:v>118.67</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-39.57</c:v>
+                  <c:v>118.48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-40.36</c:v>
+                  <c:v>118.41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3026-4BA5-A5B3-662584D103E6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -928,6 +933,97 @@
           </c:marker>
           <c:val>
             <c:numRef>
+              <c:f>Lambda_d_matrix!$C$23:$C$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>142.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>138.44999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>136.63999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>135.08000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>133.22999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>131.93</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>129.83000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>127.03</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>125.51</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>124.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>123.35</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>121.99</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>121.43</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>120.18</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>119.91</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>119.2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>118.47</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3026-4BA5-A5B3-662584D103E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>blog</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
               <c:f>Lambda_d_matrix!$L$23:$L$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -993,6 +1089,102 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3026-4BA5-A5B3-662584D103E6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$L$2:$L$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>118.65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>98.96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>77.78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>67.37</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>57.27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>47.48</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38.04</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28.92</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.22</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-6.05</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-13.02</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-18.71</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-22.65</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-24.98</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-25.76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3026-4BA5-A5B3-662584D103E6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1191,7 +1383,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
@@ -1244,6 +1436,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>sim</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -1324,79 +1519,178 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Lambda_d_matrix!$Y$2:$Y$20</c:f>
+              <c:f>Lambda_d_matrix!$P$2:$P$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>244.81</c:v>
+                  <c:v>44.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>245.91</c:v>
+                  <c:v>43.91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>246.09</c:v>
+                  <c:v>43.42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>245.33</c:v>
+                  <c:v>42.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>243.59</c:v>
+                  <c:v>41.45</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>240.77</c:v>
+                  <c:v>39.97</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>236.72</c:v>
+                  <c:v>38.19</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>231.23</c:v>
+                  <c:v>36.119999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>224.19</c:v>
+                  <c:v>33.770000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>215.5</c:v>
+                  <c:v>31.15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>204.74</c:v>
+                  <c:v>28.31</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>190.37</c:v>
+                  <c:v>25.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>171.9</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>151.66</c:v>
+                  <c:v>18.59</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>128.63</c:v>
+                  <c:v>15.04</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>101.26</c:v>
+                  <c:v>11.38</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.75</c:v>
+                  <c:v>7.63</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.33</c:v>
+                  <c:v>3.84</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.02</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-72AB-4D33-ADCA-B063982056BD}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>blog</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$P$23:$P$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>53.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.61</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.69</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.69</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>48.05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46.29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>43.17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32.47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28.67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>24.79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.170000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.42</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-72AB-4D33-ADCA-B063982056BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>blog</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1472,6 +1766,102 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-72AB-4D33-ADCA-B063982056BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Lambda_d_matrix!$Y$2:$Y$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>241.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>242.37</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>242.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>242.09</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>240.46</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>237.73</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>233.77</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>228.38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>221.48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>212.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>202.47</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>188.69</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>170.67</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150.63999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>127.64</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100.21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>68.72</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34.85</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.03</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-72AB-4D33-ADCA-B063982056BD}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2786,15 +3176,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>526675</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>202825</xdr:rowOff>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1119</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>313764</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>178172</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>100852</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>11205</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2815,16 +3205,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>414618</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135590</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>302559</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>124384</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>201706</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>110937</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>593912</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3191,37 +3581,37 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C2">
-        <v>121.72</v>
+        <v>135.63</v>
       </c>
       <c r="D2">
-        <v>121.86</v>
+        <v>135.44999999999999</v>
       </c>
       <c r="E2">
-        <v>121.29</v>
+        <v>134.31</v>
       </c>
       <c r="F2">
-        <v>119.41</v>
+        <v>131.87</v>
       </c>
       <c r="G2">
-        <v>117.07</v>
+        <v>128.97</v>
       </c>
       <c r="H2">
-        <v>115.21</v>
+        <v>126.39</v>
       </c>
       <c r="I2">
-        <v>113.66</v>
+        <v>124.32</v>
       </c>
       <c r="J2">
-        <v>112.05</v>
+        <v>122.4</v>
       </c>
       <c r="K2">
-        <v>110.36</v>
+        <v>120.51</v>
       </c>
       <c r="L2">
-        <v>108.63</v>
+        <v>118.65</v>
       </c>
       <c r="N2">
         <v>90</v>
@@ -3230,34 +3620,34 @@
         <v>0.01</v>
       </c>
       <c r="P2">
-        <v>45.58</v>
+        <v>44.06</v>
       </c>
       <c r="Q2">
-        <v>90.12</v>
+        <v>87.63</v>
       </c>
       <c r="R2">
-        <v>129.32</v>
+        <v>125.56</v>
       </c>
       <c r="S2">
-        <v>158.19999999999999</v>
+        <v>153.63999999999999</v>
       </c>
       <c r="T2">
-        <v>180.05</v>
+        <v>175.31</v>
       </c>
       <c r="U2">
-        <v>197.02</v>
+        <v>192.73</v>
       </c>
       <c r="V2">
-        <v>211.1</v>
+        <v>206.96</v>
       </c>
       <c r="W2">
-        <v>223.41</v>
+        <v>219.45</v>
       </c>
       <c r="X2">
-        <v>234.5</v>
+        <v>230.71</v>
       </c>
       <c r="Y2">
-        <v>244.81</v>
+        <v>241.18</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -3265,37 +3655,37 @@
         <v>95</v>
       </c>
       <c r="B3">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C3">
-        <v>120.17</v>
+        <v>134.13</v>
       </c>
       <c r="D3">
-        <v>118.84</v>
+        <v>132.56</v>
       </c>
       <c r="E3">
-        <v>117.14</v>
+        <v>130.41999999999999</v>
       </c>
       <c r="F3">
-        <v>114.25</v>
+        <v>127.08</v>
       </c>
       <c r="G3">
-        <v>111.01</v>
+        <v>123.34</v>
       </c>
       <c r="H3">
-        <v>108.35</v>
+        <v>120.08</v>
       </c>
       <c r="I3">
-        <v>105.95</v>
+        <v>117.26</v>
       </c>
       <c r="J3">
-        <v>103.48</v>
+        <v>114.52</v>
       </c>
       <c r="K3">
-        <v>100.89</v>
+        <v>111.77</v>
       </c>
       <c r="L3">
-        <v>98.22</v>
+        <v>109.02</v>
       </c>
       <c r="N3">
         <v>95</v>
@@ -3304,34 +3694,34 @@
         <v>0.01</v>
       </c>
       <c r="P3">
-        <v>45.41</v>
+        <v>43.91</v>
       </c>
       <c r="Q3">
-        <v>89.75</v>
+        <v>87.33</v>
       </c>
       <c r="R3">
-        <v>129.24</v>
+        <v>125.65</v>
       </c>
       <c r="S3">
-        <v>158.55000000000001</v>
+        <v>154.18</v>
       </c>
       <c r="T3">
-        <v>180.56</v>
+        <v>176.12</v>
       </c>
       <c r="U3">
-        <v>197.43</v>
+        <v>193.45</v>
       </c>
       <c r="V3">
-        <v>211.61</v>
+        <v>207.74</v>
       </c>
       <c r="W3">
-        <v>224.13</v>
+        <v>220.36</v>
       </c>
       <c r="X3">
-        <v>235.41</v>
+        <v>231.76</v>
       </c>
       <c r="Y3">
-        <v>245.91</v>
+        <v>242.37</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -3339,37 +3729,37 @@
         <v>100</v>
       </c>
       <c r="B4">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C4">
-        <v>118.64</v>
+        <v>132.65</v>
       </c>
       <c r="D4">
-        <v>115.83</v>
+        <v>129.66</v>
       </c>
       <c r="E4">
-        <v>112.99</v>
+        <v>126.49</v>
       </c>
       <c r="F4">
-        <v>109.09</v>
+        <v>122.25</v>
       </c>
       <c r="G4">
-        <v>104.88</v>
+        <v>117.65</v>
       </c>
       <c r="H4">
-        <v>101.29</v>
+        <v>113.62</v>
       </c>
       <c r="I4">
-        <v>97.92</v>
+        <v>109.99</v>
       </c>
       <c r="J4">
-        <v>94.46</v>
+        <v>106.39</v>
       </c>
       <c r="K4">
-        <v>90.86</v>
+        <v>102.7</v>
       </c>
       <c r="L4">
-        <v>87.14</v>
+        <v>98.96</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -3378,34 +3768,34 @@
         <v>0.01</v>
       </c>
       <c r="P4">
-        <v>44.9</v>
+        <v>43.42</v>
       </c>
       <c r="Q4">
-        <v>88.71</v>
+        <v>86.37</v>
       </c>
       <c r="R4">
-        <v>128.26</v>
+        <v>124.85</v>
       </c>
       <c r="S4">
-        <v>158.01</v>
+        <v>153.84</v>
       </c>
       <c r="T4">
-        <v>180.16</v>
+        <v>176.01</v>
       </c>
       <c r="U4">
-        <v>196.98</v>
+        <v>193.27</v>
       </c>
       <c r="V4">
-        <v>211.24</v>
+        <v>207.62</v>
       </c>
       <c r="W4">
-        <v>223.96</v>
+        <v>220.4</v>
       </c>
       <c r="X4">
-        <v>235.42</v>
+        <v>231.96</v>
       </c>
       <c r="Y4">
-        <v>246.09</v>
+        <v>242.7</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -3413,37 +3803,37 @@
         <v>105</v>
       </c>
       <c r="B5">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C5">
-        <v>117.14</v>
+        <v>131.19</v>
       </c>
       <c r="D5">
-        <v>112.85</v>
+        <v>126.78</v>
       </c>
       <c r="E5">
-        <v>108.86</v>
+        <v>122.55</v>
       </c>
       <c r="F5">
-        <v>103.98</v>
+        <v>117.39</v>
       </c>
       <c r="G5">
-        <v>98.78</v>
+        <v>111.87</v>
       </c>
       <c r="H5">
-        <v>94.19</v>
+        <v>106.96</v>
       </c>
       <c r="I5">
-        <v>89.8</v>
+        <v>102.41</v>
       </c>
       <c r="J5">
-        <v>85.34</v>
+        <v>97.87</v>
       </c>
       <c r="K5">
-        <v>80.709999999999994</v>
+        <v>93.19</v>
       </c>
       <c r="L5">
-        <v>75.97</v>
+        <v>88.4</v>
       </c>
       <c r="N5">
         <v>105</v>
@@ -3452,34 +3842,34 @@
         <v>0.01</v>
       </c>
       <c r="P5">
-        <v>44.04</v>
+        <v>42.6</v>
       </c>
       <c r="Q5">
-        <v>87</v>
+        <v>84.74</v>
       </c>
       <c r="R5">
-        <v>126.31</v>
+        <v>123.1</v>
       </c>
       <c r="S5">
-        <v>156.56</v>
+        <v>152.57</v>
       </c>
       <c r="T5">
-        <v>178.89</v>
+        <v>174.96</v>
       </c>
       <c r="U5">
-        <v>195.69</v>
+        <v>192.19</v>
       </c>
       <c r="V5">
-        <v>209.98</v>
+        <v>206.57</v>
       </c>
       <c r="W5">
-        <v>222.88</v>
+        <v>219.5</v>
       </c>
       <c r="X5">
-        <v>234.53</v>
+        <v>231.22</v>
       </c>
       <c r="Y5">
-        <v>245.33</v>
+        <v>242.09</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
@@ -3487,37 +3877,37 @@
         <v>110</v>
       </c>
       <c r="B6">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C6">
-        <v>115.67</v>
+        <v>129.76</v>
       </c>
       <c r="D6">
-        <v>109.93</v>
+        <v>123.96</v>
       </c>
       <c r="E6">
-        <v>104.72</v>
+        <v>118.58</v>
       </c>
       <c r="F6">
-        <v>98.95</v>
+        <v>112.53</v>
       </c>
       <c r="G6">
-        <v>92.79</v>
+        <v>106.08</v>
       </c>
       <c r="H6">
-        <v>87.19</v>
+        <v>100.19</v>
       </c>
       <c r="I6">
-        <v>81.790000000000006</v>
+        <v>94.66</v>
       </c>
       <c r="J6">
-        <v>76.349999999999994</v>
+        <v>89.15</v>
       </c>
       <c r="K6">
-        <v>70.790000000000006</v>
+        <v>83.53</v>
       </c>
       <c r="L6">
-        <v>65.09</v>
+        <v>77.78</v>
       </c>
       <c r="N6">
         <v>110</v>
@@ -3526,34 +3916,34 @@
         <v>0.01</v>
       </c>
       <c r="P6">
-        <v>42.84</v>
+        <v>41.45</v>
       </c>
       <c r="Q6">
-        <v>84.65</v>
+        <v>82.48</v>
       </c>
       <c r="R6">
-        <v>123.31</v>
+        <v>120.32</v>
       </c>
       <c r="S6">
-        <v>154.11000000000001</v>
+        <v>150.31</v>
       </c>
       <c r="T6">
-        <v>176.72</v>
+        <v>172.96</v>
       </c>
       <c r="U6">
-        <v>193.55</v>
+        <v>190.19</v>
       </c>
       <c r="V6">
-        <v>207.84</v>
+        <v>204.56</v>
       </c>
       <c r="W6">
-        <v>220.83</v>
+        <v>217.56</v>
       </c>
       <c r="X6">
-        <v>232.68</v>
+        <v>229.48</v>
       </c>
       <c r="Y6">
-        <v>243.59</v>
+        <v>240.46</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -3561,37 +3951,37 @@
         <v>115</v>
       </c>
       <c r="B7">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C7">
-        <v>114.25</v>
+        <v>128.37</v>
       </c>
       <c r="D7">
-        <v>107.1</v>
+        <v>121.2</v>
       </c>
       <c r="E7">
-        <v>100.62</v>
+        <v>114.61</v>
       </c>
       <c r="F7">
-        <v>93.99</v>
+        <v>107.72</v>
       </c>
       <c r="G7">
-        <v>86.93</v>
+        <v>100.36</v>
       </c>
       <c r="H7">
-        <v>80.36</v>
+        <v>93.5</v>
       </c>
       <c r="I7">
-        <v>73.97</v>
+        <v>86.99</v>
       </c>
       <c r="J7">
-        <v>67.58</v>
+        <v>80.53</v>
       </c>
       <c r="K7">
-        <v>61.12</v>
+        <v>74.010000000000005</v>
       </c>
       <c r="L7">
-        <v>54.55</v>
+        <v>67.37</v>
       </c>
       <c r="N7">
         <v>115</v>
@@ -3600,34 +3990,34 @@
         <v>0.01</v>
       </c>
       <c r="P7">
-        <v>41.32</v>
+        <v>39.97</v>
       </c>
       <c r="Q7">
-        <v>81.66</v>
+        <v>79.58</v>
       </c>
       <c r="R7">
-        <v>119.24</v>
+        <v>116.47</v>
       </c>
       <c r="S7">
-        <v>150.54</v>
+        <v>146.96</v>
       </c>
       <c r="T7">
-        <v>173.59</v>
+        <v>169.95</v>
       </c>
       <c r="U7">
-        <v>190.52</v>
+        <v>187.28</v>
       </c>
       <c r="V7">
-        <v>204.78</v>
+        <v>201.6</v>
       </c>
       <c r="W7">
-        <v>217.74</v>
+        <v>214.57</v>
       </c>
       <c r="X7">
-        <v>229.74</v>
+        <v>226.62</v>
       </c>
       <c r="Y7">
-        <v>240.77</v>
+        <v>237.73</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
@@ -3635,37 +4025,37 @@
         <v>120</v>
       </c>
       <c r="B8">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C8">
-        <v>112.88</v>
+        <v>127.04</v>
       </c>
       <c r="D8">
-        <v>104.37</v>
+        <v>118.54</v>
       </c>
       <c r="E8">
-        <v>96.62</v>
+        <v>110.7</v>
       </c>
       <c r="F8">
-        <v>89.09</v>
+        <v>102.96</v>
       </c>
       <c r="G8">
-        <v>81.2</v>
+        <v>94.78</v>
       </c>
       <c r="H8">
-        <v>73.7</v>
+        <v>86.97</v>
       </c>
       <c r="I8">
-        <v>66.38</v>
+        <v>79.52</v>
       </c>
       <c r="J8">
-        <v>59.06</v>
+        <v>72.14</v>
       </c>
       <c r="K8">
-        <v>51.71</v>
+        <v>64.73</v>
       </c>
       <c r="L8">
-        <v>44.32</v>
+        <v>57.27</v>
       </c>
       <c r="N8">
         <v>120</v>
@@ -3674,34 +4064,34 @@
         <v>0.01</v>
       </c>
       <c r="P8">
-        <v>39.479999999999997</v>
+        <v>38.19</v>
       </c>
       <c r="Q8">
-        <v>78.05</v>
+        <v>76.08</v>
       </c>
       <c r="R8">
-        <v>114.19</v>
+        <v>111.61</v>
       </c>
       <c r="S8">
-        <v>145.63999999999999</v>
+        <v>142.34</v>
       </c>
       <c r="T8">
-        <v>169.31</v>
+        <v>165.81</v>
       </c>
       <c r="U8">
-        <v>186.52</v>
+        <v>183.39</v>
       </c>
       <c r="V8">
-        <v>200.72</v>
+        <v>197.66</v>
       </c>
       <c r="W8">
-        <v>213.58</v>
+        <v>210.52</v>
       </c>
       <c r="X8">
-        <v>225.57</v>
+        <v>222.53</v>
       </c>
       <c r="Y8">
-        <v>236.72</v>
+        <v>233.77</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
@@ -3709,37 +4099,37 @@
         <v>125</v>
       </c>
       <c r="B9">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C9">
-        <v>111.58</v>
+        <v>125.78</v>
       </c>
       <c r="D9">
-        <v>101.77</v>
+        <v>116</v>
       </c>
       <c r="E9">
-        <v>92.75</v>
+        <v>106.92</v>
       </c>
       <c r="F9">
-        <v>84.19</v>
+        <v>98.22</v>
       </c>
       <c r="G9">
-        <v>75.569999999999993</v>
+        <v>89.33</v>
       </c>
       <c r="H9">
-        <v>67.209999999999994</v>
+        <v>80.64</v>
       </c>
       <c r="I9">
-        <v>59.02</v>
+        <v>72.3</v>
       </c>
       <c r="J9">
-        <v>50.83</v>
+        <v>64.03</v>
       </c>
       <c r="K9">
-        <v>42.62</v>
+        <v>55.76</v>
       </c>
       <c r="L9">
-        <v>34.409999999999997</v>
+        <v>47.48</v>
       </c>
       <c r="N9">
         <v>125</v>
@@ -3748,34 +4138,34 @@
         <v>0.01</v>
       </c>
       <c r="P9">
-        <v>37.35</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="Q9">
-        <v>73.86</v>
+        <v>72</v>
       </c>
       <c r="R9">
-        <v>108.2</v>
+        <v>105.8</v>
       </c>
       <c r="S9">
-        <v>139.16</v>
+        <v>136.18</v>
       </c>
       <c r="T9">
-        <v>163.6</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="U9">
-        <v>181.34</v>
+        <v>178.37</v>
       </c>
       <c r="V9">
-        <v>195.57</v>
+        <v>192.65</v>
       </c>
       <c r="W9">
-        <v>208.28</v>
+        <v>205.34</v>
       </c>
       <c r="X9">
-        <v>220.12</v>
+        <v>217.18</v>
       </c>
       <c r="Y9">
-        <v>231.23</v>
+        <v>228.38</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
@@ -3783,37 +4173,37 @@
         <v>130</v>
       </c>
       <c r="B10">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C10">
-        <v>110.36</v>
+        <v>124.58</v>
       </c>
       <c r="D10">
-        <v>99.31</v>
+        <v>113.6</v>
       </c>
       <c r="E10">
-        <v>89.07</v>
+        <v>103.32</v>
       </c>
       <c r="F10">
-        <v>79.37</v>
+        <v>93.53</v>
       </c>
       <c r="G10">
-        <v>69.94</v>
+        <v>83.92</v>
       </c>
       <c r="H10">
-        <v>60.81</v>
+        <v>74.44</v>
       </c>
       <c r="I10">
-        <v>51.84</v>
+        <v>65.31</v>
       </c>
       <c r="J10">
-        <v>42.84</v>
+        <v>56.22</v>
       </c>
       <c r="K10">
-        <v>33.799999999999997</v>
+        <v>47.13</v>
       </c>
       <c r="L10">
-        <v>24.78</v>
+        <v>38.04</v>
       </c>
       <c r="N10">
         <v>130</v>
@@ -3822,34 +4212,34 @@
         <v>0.01</v>
       </c>
       <c r="P10">
-        <v>34.93</v>
+        <v>33.770000000000003</v>
       </c>
       <c r="Q10">
-        <v>69.11</v>
+        <v>67.37</v>
       </c>
       <c r="R10">
-        <v>101.36</v>
+        <v>99.14</v>
       </c>
       <c r="S10">
-        <v>131.09</v>
+        <v>128.4</v>
       </c>
       <c r="T10">
-        <v>156.02000000000001</v>
+        <v>153.02000000000001</v>
       </c>
       <c r="U10">
-        <v>174.63</v>
+        <v>171.89</v>
       </c>
       <c r="V10">
-        <v>189.07</v>
+        <v>186.36</v>
       </c>
       <c r="W10">
-        <v>201.67</v>
+        <v>198.93</v>
       </c>
       <c r="X10">
-        <v>213.27</v>
+        <v>210.51</v>
       </c>
       <c r="Y10">
-        <v>224.19</v>
+        <v>221.48</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
@@ -3857,37 +4247,37 @@
         <v>135</v>
       </c>
       <c r="B11">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C11">
-        <v>109.22</v>
+        <v>123.48</v>
       </c>
       <c r="D11">
-        <v>97.02</v>
+        <v>111.37</v>
       </c>
       <c r="E11">
-        <v>85.61</v>
+        <v>99.94</v>
       </c>
       <c r="F11">
-        <v>74.760000000000005</v>
+        <v>89.04</v>
       </c>
       <c r="G11">
-        <v>64.290000000000006</v>
+        <v>78.48</v>
       </c>
       <c r="H11">
-        <v>54.34</v>
+        <v>68.25</v>
       </c>
       <c r="I11">
-        <v>44.72</v>
+        <v>58.41</v>
       </c>
       <c r="J11">
-        <v>35.03</v>
+        <v>48.61</v>
       </c>
       <c r="K11">
-        <v>25.27</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="L11">
-        <v>15.5</v>
+        <v>28.92</v>
       </c>
       <c r="N11">
         <v>135</v>
@@ -3896,34 +4286,34 @@
         <v>0.01</v>
       </c>
       <c r="P11">
-        <v>32.24</v>
+        <v>31.15</v>
       </c>
       <c r="Q11">
-        <v>63.84</v>
+        <v>62.22</v>
       </c>
       <c r="R11">
-        <v>93.72</v>
+        <v>91.7</v>
       </c>
       <c r="S11">
-        <v>121.64</v>
+        <v>119.23</v>
       </c>
       <c r="T11">
-        <v>146.24</v>
+        <v>143.57</v>
       </c>
       <c r="U11">
-        <v>165.73</v>
+        <v>163.31</v>
       </c>
       <c r="V11">
-        <v>180.71</v>
+        <v>178.31</v>
       </c>
       <c r="W11">
-        <v>193.4</v>
+        <v>190.92</v>
       </c>
       <c r="X11">
-        <v>204.84</v>
+        <v>202.3</v>
       </c>
       <c r="Y11">
-        <v>215.5</v>
+        <v>212.95</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
@@ -3931,37 +4321,37 @@
         <v>140</v>
       </c>
       <c r="B12">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C12">
-        <v>108.19</v>
+        <v>122.46</v>
       </c>
       <c r="D12">
-        <v>94.92</v>
+        <v>109.31</v>
       </c>
       <c r="E12">
-        <v>82.41</v>
+        <v>96.81</v>
       </c>
       <c r="F12">
-        <v>70.459999999999994</v>
+        <v>84.85</v>
       </c>
       <c r="G12">
-        <v>58.91</v>
+        <v>73.239999999999995</v>
       </c>
       <c r="H12">
-        <v>47.85</v>
+        <v>62.01</v>
       </c>
       <c r="I12">
-        <v>37.44</v>
+        <v>51.39</v>
       </c>
       <c r="J12">
-        <v>27.21</v>
+        <v>41.02</v>
       </c>
       <c r="K12">
-        <v>16.899999999999999</v>
+        <v>30.59</v>
       </c>
       <c r="L12">
-        <v>6.55</v>
+        <v>20.12</v>
       </c>
       <c r="N12">
         <v>140</v>
@@ -3970,34 +4360,34 @@
         <v>0.01</v>
       </c>
       <c r="P12">
-        <v>29.31</v>
+        <v>28.31</v>
       </c>
       <c r="Q12">
-        <v>58.09</v>
+        <v>56.59</v>
       </c>
       <c r="R12">
-        <v>85.36</v>
+        <v>83.52</v>
       </c>
       <c r="S12">
-        <v>111.03</v>
+        <v>108.87</v>
       </c>
       <c r="T12">
-        <v>134.55000000000001</v>
+        <v>132.13</v>
       </c>
       <c r="U12">
-        <v>154.19999999999999</v>
+        <v>151.93</v>
       </c>
       <c r="V12">
-        <v>169.57</v>
+        <v>167.59</v>
       </c>
       <c r="W12">
-        <v>182.63</v>
+        <v>180.58</v>
       </c>
       <c r="X12">
-        <v>194.19</v>
+        <v>192</v>
       </c>
       <c r="Y12">
-        <v>204.74</v>
+        <v>202.47</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
@@ -4005,37 +4395,37 @@
         <v>145</v>
       </c>
       <c r="B13">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C13">
-        <v>107.25</v>
+        <v>121.54</v>
       </c>
       <c r="D13">
-        <v>93.02</v>
+        <v>107.46</v>
       </c>
       <c r="E13">
-        <v>79.489999999999995</v>
+        <v>93.97</v>
       </c>
       <c r="F13">
-        <v>66.540000000000006</v>
+        <v>81.010000000000005</v>
       </c>
       <c r="G13">
-        <v>53.96</v>
+        <v>68.39</v>
       </c>
       <c r="H13">
-        <v>41.78</v>
+        <v>56.13</v>
       </c>
       <c r="I13">
-        <v>30.24</v>
+        <v>44.39</v>
       </c>
       <c r="J13">
-        <v>19.13</v>
+        <v>33.19</v>
       </c>
       <c r="K13">
-        <v>8.19</v>
+        <v>22.17</v>
       </c>
       <c r="L13">
-        <v>-2.61</v>
+        <v>11.22</v>
       </c>
       <c r="N13">
         <v>145</v>
@@ -4044,34 +4434,34 @@
         <v>0.01</v>
       </c>
       <c r="P13">
-        <v>26.15</v>
+        <v>25.25</v>
       </c>
       <c r="Q13">
-        <v>51.89</v>
+        <v>50.51</v>
       </c>
       <c r="R13">
-        <v>76.319999999999993</v>
+        <v>74.67</v>
       </c>
       <c r="S13">
-        <v>99.42</v>
+        <v>97.51</v>
       </c>
       <c r="T13">
-        <v>121.11</v>
+        <v>118.96</v>
       </c>
       <c r="U13">
-        <v>140.34</v>
+        <v>138.16999999999999</v>
       </c>
       <c r="V13">
-        <v>155.69</v>
+        <v>153.94</v>
       </c>
       <c r="W13">
-        <v>168.38</v>
+        <v>166.77</v>
       </c>
       <c r="X13">
-        <v>179.79</v>
+        <v>178.17</v>
       </c>
       <c r="Y13">
-        <v>190.37</v>
+        <v>188.69</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -4079,37 +4469,37 @@
         <v>150</v>
       </c>
       <c r="B14">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C14">
-        <v>106.43</v>
+        <v>120.73</v>
       </c>
       <c r="D14">
-        <v>91.33</v>
+        <v>105.81</v>
       </c>
       <c r="E14">
-        <v>76.91</v>
+        <v>91.43</v>
       </c>
       <c r="F14">
-        <v>63.04</v>
+        <v>77.569999999999993</v>
       </c>
       <c r="G14">
-        <v>49.53</v>
+        <v>64.040000000000006</v>
       </c>
       <c r="H14">
-        <v>36.35</v>
+        <v>50.83</v>
       </c>
       <c r="I14">
-        <v>23.65</v>
+        <v>38.01</v>
       </c>
       <c r="J14">
-        <v>11.5</v>
+        <v>25.74</v>
       </c>
       <c r="K14">
-        <v>-0.35</v>
+        <v>13.8</v>
       </c>
       <c r="L14">
-        <v>-11.97</v>
+        <v>2.08</v>
       </c>
       <c r="N14">
         <v>150</v>
@@ -4118,34 +4508,34 @@
         <v>0.01</v>
       </c>
       <c r="P14">
-        <v>22.79</v>
+        <v>22</v>
       </c>
       <c r="Q14">
-        <v>45.29</v>
+        <v>44.04</v>
       </c>
       <c r="R14">
-        <v>66.69</v>
+        <v>65.2</v>
       </c>
       <c r="S14">
-        <v>86.95</v>
+        <v>85.26</v>
       </c>
       <c r="T14">
-        <v>106.23</v>
+        <v>104.35</v>
       </c>
       <c r="U14">
-        <v>124.11</v>
+        <v>122.12</v>
       </c>
       <c r="V14">
-        <v>139.53</v>
+        <v>137.77000000000001</v>
       </c>
       <c r="W14">
-        <v>151.76</v>
+        <v>150.34</v>
       </c>
       <c r="X14">
-        <v>162.29</v>
+        <v>161</v>
       </c>
       <c r="Y14">
-        <v>171.9</v>
+        <v>170.67</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
@@ -4153,37 +4543,37 @@
         <v>155</v>
       </c>
       <c r="B15">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C15">
-        <v>105.73</v>
+        <v>120.03</v>
       </c>
       <c r="D15">
-        <v>89.89</v>
+        <v>104.4</v>
       </c>
       <c r="E15">
-        <v>74.680000000000007</v>
+        <v>89.24</v>
       </c>
       <c r="F15">
-        <v>60.01</v>
+        <v>74.58</v>
       </c>
       <c r="G15">
-        <v>45.68</v>
+        <v>60.26</v>
       </c>
       <c r="H15">
-        <v>31.65</v>
+        <v>46.22</v>
       </c>
       <c r="I15">
-        <v>17.98</v>
+        <v>32.5</v>
       </c>
       <c r="J15">
-        <v>4.82</v>
+        <v>19.22</v>
       </c>
       <c r="K15">
-        <v>-7.85</v>
+        <v>6.43</v>
       </c>
       <c r="L15">
-        <v>-20.23</v>
+        <v>-6.05</v>
       </c>
       <c r="N15">
         <v>155</v>
@@ -4192,34 +4582,34 @@
         <v>0.01</v>
       </c>
       <c r="P15">
-        <v>19.25</v>
+        <v>18.59</v>
       </c>
       <c r="Q15">
-        <v>38.340000000000003</v>
+        <v>37.229999999999997</v>
       </c>
       <c r="R15">
-        <v>56.52</v>
+        <v>55.19</v>
       </c>
       <c r="S15">
-        <v>73.75</v>
+        <v>72.260000000000005</v>
       </c>
       <c r="T15">
-        <v>90.23</v>
+        <v>88.6</v>
       </c>
       <c r="U15">
-        <v>105.91</v>
+        <v>104.16</v>
       </c>
       <c r="V15">
-        <v>120.36</v>
+        <v>118.62</v>
       </c>
       <c r="W15">
-        <v>132.74</v>
+        <v>131.34</v>
       </c>
       <c r="X15">
-        <v>142.87</v>
+        <v>141.72</v>
       </c>
       <c r="Y15">
-        <v>151.66</v>
+        <v>150.63999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
@@ -4227,37 +4617,37 @@
         <v>160</v>
       </c>
       <c r="B16">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C16">
-        <v>105.15</v>
+        <v>119.46</v>
       </c>
       <c r="D16">
-        <v>88.69</v>
+        <v>103.23</v>
       </c>
       <c r="E16">
-        <v>72.819999999999993</v>
+        <v>87.41</v>
       </c>
       <c r="F16">
-        <v>57.47</v>
+        <v>72.08</v>
       </c>
       <c r="G16">
-        <v>42.49</v>
+        <v>57.1</v>
       </c>
       <c r="H16">
-        <v>27.85</v>
+        <v>42.46</v>
       </c>
       <c r="I16">
-        <v>13.48</v>
+        <v>28.09</v>
       </c>
       <c r="J16">
-        <v>-0.56999999999999995</v>
+        <v>13.98</v>
       </c>
       <c r="K16">
-        <v>-14.16</v>
+        <v>0.24</v>
       </c>
       <c r="L16">
-        <v>-27.3</v>
+        <v>-13.02</v>
       </c>
       <c r="N16">
         <v>160</v>
@@ -4266,34 +4656,34 @@
         <v>0.01</v>
       </c>
       <c r="P16">
-        <v>15.57</v>
+        <v>15.04</v>
       </c>
       <c r="Q16">
-        <v>31.08</v>
+        <v>30.12</v>
       </c>
       <c r="R16">
-        <v>45.87</v>
+        <v>44.72</v>
       </c>
       <c r="S16">
-        <v>59.92</v>
+        <v>58.63</v>
       </c>
       <c r="T16">
-        <v>73.38</v>
+        <v>71.959999999999994</v>
       </c>
       <c r="U16">
-        <v>86.41</v>
+        <v>84.89</v>
       </c>
       <c r="V16">
-        <v>98.87</v>
+        <v>97.29</v>
       </c>
       <c r="W16">
-        <v>110.35</v>
+        <v>108.84</v>
       </c>
       <c r="X16">
-        <v>120.23</v>
+        <v>119.05</v>
       </c>
       <c r="Y16">
-        <v>128.63</v>
+        <v>127.64</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -4301,37 +4691,37 @@
         <v>165</v>
       </c>
       <c r="B17">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C17">
-        <v>104.69</v>
+        <v>119</v>
       </c>
       <c r="D17">
-        <v>87.76</v>
+        <v>102.32</v>
       </c>
       <c r="E17">
-        <v>71.36</v>
+        <v>85.97</v>
       </c>
       <c r="F17">
-        <v>55.47</v>
+        <v>70.11</v>
       </c>
       <c r="G17">
-        <v>40.04</v>
+        <v>54.68</v>
       </c>
       <c r="H17">
-        <v>24.92</v>
+        <v>39.57</v>
       </c>
       <c r="I17">
-        <v>10.02</v>
+        <v>24.67</v>
       </c>
       <c r="J17">
-        <v>-4.6900000000000004</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="K17">
-        <v>-19.11</v>
+        <v>-4.5599999999999996</v>
       </c>
       <c r="L17">
-        <v>-33.11</v>
+        <v>-18.71</v>
       </c>
       <c r="N17">
         <v>165</v>
@@ -4340,34 +4730,34 @@
         <v>0.01</v>
       </c>
       <c r="P17">
-        <v>11.77</v>
+        <v>11.38</v>
       </c>
       <c r="Q17">
-        <v>23.58</v>
+        <v>22.77</v>
       </c>
       <c r="R17">
-        <v>34.840000000000003</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="S17">
-        <v>45.56</v>
+        <v>44.48</v>
       </c>
       <c r="T17">
-        <v>55.91</v>
+        <v>54.73</v>
       </c>
       <c r="U17">
-        <v>65.97</v>
+        <v>64.7</v>
       </c>
       <c r="V17">
-        <v>75.69</v>
+        <v>74.349999999999994</v>
       </c>
       <c r="W17">
-        <v>85</v>
+        <v>83.62</v>
       </c>
       <c r="X17">
-        <v>93.67</v>
+        <v>92.36</v>
       </c>
       <c r="Y17">
-        <v>101.26</v>
+        <v>100.21</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -4375,37 +4765,37 @@
         <v>170</v>
       </c>
       <c r="B18">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C18">
-        <v>104.36</v>
+        <v>118.67</v>
       </c>
       <c r="D18">
-        <v>87.1</v>
+        <v>101.66</v>
       </c>
       <c r="E18">
-        <v>70.3</v>
+        <v>84.93</v>
       </c>
       <c r="F18">
-        <v>54.07</v>
+        <v>68.73</v>
       </c>
       <c r="G18">
-        <v>38.299999999999997</v>
+        <v>52.97</v>
       </c>
       <c r="H18">
-        <v>22.81</v>
+        <v>37.49</v>
       </c>
       <c r="I18">
-        <v>7.51</v>
+        <v>22.2</v>
       </c>
       <c r="J18">
-        <v>-7.62</v>
+        <v>7.07</v>
       </c>
       <c r="K18">
-        <v>-22.55</v>
+        <v>-7.91</v>
       </c>
       <c r="L18">
-        <v>-37.18</v>
+        <v>-22.65</v>
       </c>
       <c r="N18">
         <v>170</v>
@@ -4414,34 +4804,34 @@
         <v>0.01</v>
       </c>
       <c r="P18">
-        <v>7.9</v>
+        <v>7.63</v>
       </c>
       <c r="Q18">
-        <v>15.86</v>
+        <v>15.27</v>
       </c>
       <c r="R18">
-        <v>23.5</v>
+        <v>22.74</v>
       </c>
       <c r="S18">
-        <v>30.78</v>
+        <v>29.94</v>
       </c>
       <c r="T18">
-        <v>37.89</v>
+        <v>36.979999999999997</v>
       </c>
       <c r="U18">
-        <v>44.72</v>
+        <v>43.77</v>
       </c>
       <c r="V18">
-        <v>51.35</v>
+        <v>50.34</v>
       </c>
       <c r="W18">
-        <v>57.76</v>
+        <v>56.71</v>
       </c>
       <c r="X18">
-        <v>63.91</v>
+        <v>62.86</v>
       </c>
       <c r="Y18">
-        <v>69.75</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -4449,37 +4839,37 @@
         <v>175</v>
       </c>
       <c r="B19">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C19">
-        <v>104.17</v>
+        <v>118.48</v>
       </c>
       <c r="D19">
-        <v>86.71</v>
+        <v>101.27</v>
       </c>
       <c r="E19">
-        <v>69.650000000000006</v>
+        <v>84.29</v>
       </c>
       <c r="F19">
-        <v>53.26</v>
+        <v>67.94</v>
       </c>
       <c r="G19">
-        <v>37.26</v>
+        <v>51.96</v>
       </c>
       <c r="H19">
-        <v>21.51</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="I19">
-        <v>5.95</v>
+        <v>20.68</v>
       </c>
       <c r="J19">
-        <v>-9.4600000000000009</v>
+        <v>5.29</v>
       </c>
       <c r="K19">
-        <v>-24.68</v>
+        <v>-9.9600000000000009</v>
       </c>
       <c r="L19">
-        <v>-39.57</v>
+        <v>-24.98</v>
       </c>
       <c r="N19">
         <v>175</v>
@@ -4488,34 +4878,34 @@
         <v>0.01</v>
       </c>
       <c r="P19">
-        <v>3.97</v>
+        <v>3.84</v>
       </c>
       <c r="Q19">
-        <v>7.97</v>
+        <v>7.67</v>
       </c>
       <c r="R19">
-        <v>11.87</v>
+        <v>11.42</v>
       </c>
       <c r="S19">
-        <v>15.6</v>
+        <v>15.08</v>
       </c>
       <c r="T19">
-        <v>19.27</v>
+        <v>18.73</v>
       </c>
       <c r="U19">
-        <v>22.76</v>
+        <v>22.22</v>
       </c>
       <c r="V19">
-        <v>26.07</v>
+        <v>25.53</v>
       </c>
       <c r="W19">
-        <v>29.25</v>
+        <v>28.73</v>
       </c>
       <c r="X19">
-        <v>32.33</v>
+        <v>31.83</v>
       </c>
       <c r="Y19">
-        <v>35.33</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -4523,37 +4913,37 @@
         <v>180</v>
       </c>
       <c r="B20">
-        <v>121.82</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C20">
-        <v>104.1</v>
+        <v>118.41</v>
       </c>
       <c r="D20">
-        <v>86.58</v>
+        <v>101.14</v>
       </c>
       <c r="E20">
-        <v>69.430000000000007</v>
+        <v>84.08</v>
       </c>
       <c r="F20">
-        <v>52.99</v>
+        <v>67.680000000000007</v>
       </c>
       <c r="G20">
-        <v>36.909999999999997</v>
+        <v>51.64</v>
       </c>
       <c r="H20">
-        <v>21.05</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="I20">
-        <v>5.36</v>
+        <v>20.14</v>
       </c>
       <c r="J20">
-        <v>-10.130000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="K20">
-        <v>-25.42</v>
+        <v>-10.66</v>
       </c>
       <c r="L20">
-        <v>-40.36</v>
+        <v>-25.76</v>
       </c>
       <c r="N20">
         <v>180</v>
@@ -4568,28 +4958,28 @@
         <v>0.02</v>
       </c>
       <c r="R20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="S20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="T20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="U20">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="V20">
         <v>0.03</v>
       </c>
       <c r="W20">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="X20">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Y20">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -6072,47 +6462,47 @@
       </c>
       <c r="B43">
         <f>B2-B23</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C43">
         <f t="shared" ref="C43:L43" si="0">C2-C23</f>
-        <v>-20.430000000000007</v>
+        <v>-6.5200000000000102</v>
       </c>
       <c r="D43">
         <f t="shared" si="0"/>
-        <v>-19.829999999999998</v>
+        <v>-6.2400000000000091</v>
       </c>
       <c r="E43">
         <f t="shared" si="0"/>
-        <v>-18.320000000000007</v>
+        <v>-5.3000000000000114</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
-        <v>-17.950000000000017</v>
+        <v>-5.4900000000000091</v>
       </c>
       <c r="G43">
         <f t="shared" si="0"/>
-        <v>-18.150000000000006</v>
+        <v>-6.25</v>
       </c>
       <c r="H43">
         <f t="shared" si="0"/>
-        <v>-17.570000000000007</v>
+        <v>-6.3900000000000006</v>
       </c>
       <c r="I43">
         <f t="shared" si="0"/>
-        <v>-16.920000000000016</v>
+        <v>-6.2600000000000193</v>
       </c>
       <c r="J43">
         <f t="shared" si="0"/>
-        <v>-16.320000000000007</v>
+        <v>-5.9699999999999989</v>
       </c>
       <c r="K43">
         <f t="shared" si="0"/>
-        <v>-14.75</v>
+        <v>-4.5999999999999943</v>
       </c>
       <c r="L43">
         <f t="shared" si="0"/>
-        <v>-14.280000000000001</v>
+        <v>-4.2599999999999909</v>
       </c>
       <c r="O43">
         <f>O2-O23</f>
@@ -6120,43 +6510,43 @@
       </c>
       <c r="P43">
         <f t="shared" ref="P43:X43" si="1">P2-P23</f>
-        <v>-8.3800000000000026</v>
+        <v>-9.8999999999999986</v>
       </c>
       <c r="Q43">
         <f t="shared" si="1"/>
-        <v>-13.97999999999999</v>
+        <v>-16.47</v>
       </c>
       <c r="R43">
         <f t="shared" si="1"/>
-        <v>-11.969999999999999</v>
+        <v>-15.72999999999999</v>
       </c>
       <c r="S43">
         <f t="shared" si="1"/>
-        <v>-8.7600000000000193</v>
+        <v>-13.320000000000022</v>
       </c>
       <c r="T43">
         <f t="shared" si="1"/>
-        <v>-5.4899999999999807</v>
+        <v>-10.22999999999999</v>
       </c>
       <c r="U43">
         <f t="shared" si="1"/>
-        <v>-8.4099999999999966</v>
+        <v>-12.700000000000017</v>
       </c>
       <c r="V43">
         <f t="shared" si="1"/>
-        <v>-12.450000000000017</v>
+        <v>-16.590000000000003</v>
       </c>
       <c r="W43">
         <f t="shared" si="1"/>
-        <v>-18.069999999999993</v>
+        <v>-22.03</v>
       </c>
       <c r="X43">
         <f t="shared" si="1"/>
-        <v>-18.889999999999986</v>
+        <v>-22.679999999999978</v>
       </c>
       <c r="Y43">
         <f>Y2-Y23</f>
-        <v>-18.629999999999995</v>
+        <v>-22.259999999999991</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -6165,47 +6555,47 @@
       </c>
       <c r="B44">
         <f t="shared" ref="B44:L44" si="2">B3-B24</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C44">
         <f t="shared" si="2"/>
-        <v>-19.989999999999995</v>
+        <v>-6.0300000000000011</v>
       </c>
       <c r="D44">
         <f t="shared" si="2"/>
-        <v>-19.609999999999985</v>
+        <v>-5.8899999999999864</v>
       </c>
       <c r="E44">
         <f t="shared" si="2"/>
-        <v>-19.11</v>
+        <v>-5.8300000000000125</v>
       </c>
       <c r="F44">
         <f t="shared" si="2"/>
-        <v>-19.090000000000003</v>
+        <v>-6.2600000000000051</v>
       </c>
       <c r="G44">
         <f t="shared" si="2"/>
-        <v>-18.959999999999994</v>
+        <v>-6.6299999999999955</v>
       </c>
       <c r="H44">
         <f t="shared" si="2"/>
-        <v>-18.260000000000005</v>
+        <v>-6.5300000000000011</v>
       </c>
       <c r="I44">
         <f t="shared" si="2"/>
-        <v>-17.25</v>
+        <v>-5.9399999999999977</v>
       </c>
       <c r="J44">
         <f t="shared" si="2"/>
-        <v>-16.989999999999995</v>
+        <v>-5.9500000000000028</v>
       </c>
       <c r="K44">
         <f t="shared" si="2"/>
-        <v>-16.319999999999993</v>
+        <v>-5.4399999999999977</v>
       </c>
       <c r="L44">
         <f t="shared" si="2"/>
-        <v>-15.739999999999995</v>
+        <v>-4.9399999999999977</v>
       </c>
       <c r="O44">
         <f t="shared" ref="O44:Y44" si="3">O3-O24</f>
@@ -6213,43 +6603,43 @@
       </c>
       <c r="P44">
         <f t="shared" si="3"/>
-        <v>-8.740000000000002</v>
+        <v>-10.240000000000002</v>
       </c>
       <c r="Q44">
         <f t="shared" si="3"/>
-        <v>-14.599999999999994</v>
+        <v>-17.019999999999996</v>
       </c>
       <c r="R44">
         <f t="shared" si="3"/>
-        <v>-12.560000000000002</v>
+        <v>-16.150000000000006</v>
       </c>
       <c r="S44">
         <f t="shared" si="3"/>
-        <v>-9.1599999999999966</v>
+        <v>-13.530000000000001</v>
       </c>
       <c r="T44">
         <f t="shared" si="3"/>
-        <v>-5.960000000000008</v>
+        <v>-10.400000000000006</v>
       </c>
       <c r="U44">
         <f t="shared" si="3"/>
-        <v>-7.3899999999999864</v>
+        <v>-11.370000000000005</v>
       </c>
       <c r="V44">
         <f t="shared" si="3"/>
-        <v>-11.189999999999998</v>
+        <v>-15.060000000000002</v>
       </c>
       <c r="W44">
         <f t="shared" si="3"/>
-        <v>-16.289999999999992</v>
+        <v>-20.059999999999974</v>
       </c>
       <c r="X44">
         <f t="shared" si="3"/>
-        <v>-16.810000000000002</v>
+        <v>-20.460000000000008</v>
       </c>
       <c r="Y44">
         <f t="shared" si="3"/>
-        <v>-16.000000000000028</v>
+        <v>-19.54000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
@@ -6258,47 +6648,47 @@
       </c>
       <c r="B45">
         <f t="shared" ref="B45:L45" si="4">B4-B25</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C45">
         <f t="shared" si="4"/>
-        <v>-19.809999999999988</v>
+        <v>-5.7999999999999829</v>
       </c>
       <c r="D45">
         <f t="shared" si="4"/>
-        <v>-19.500000000000014</v>
+        <v>-5.6700000000000159</v>
       </c>
       <c r="E45">
         <f t="shared" si="4"/>
-        <v>-18.769999999999996</v>
+        <v>-5.269999999999996</v>
       </c>
       <c r="F45">
         <f t="shared" si="4"/>
-        <v>-19.060000000000002</v>
+        <v>-5.9000000000000057</v>
       </c>
       <c r="G45">
         <f t="shared" si="4"/>
-        <v>-19.03</v>
+        <v>-6.2599999999999909</v>
       </c>
       <c r="H45">
         <f t="shared" si="4"/>
-        <v>-19.459999999999994</v>
+        <v>-7.1299999999999955</v>
       </c>
       <c r="I45">
         <f t="shared" si="4"/>
-        <v>-18.489999999999995</v>
+        <v>-6.4200000000000017</v>
       </c>
       <c r="J45">
         <f t="shared" si="4"/>
-        <v>-18.180000000000007</v>
+        <v>-6.25</v>
       </c>
       <c r="K45">
         <f t="shared" si="4"/>
-        <v>-18.010000000000005</v>
+        <v>-6.1700000000000017</v>
       </c>
       <c r="L45">
         <f t="shared" si="4"/>
-        <v>-17.959999999999994</v>
+        <v>-6.1400000000000006</v>
       </c>
       <c r="O45">
         <f t="shared" ref="O45:Y45" si="5">O4-O25</f>
@@ -6306,43 +6696,43 @@
       </c>
       <c r="P45">
         <f t="shared" si="5"/>
-        <v>-9.5500000000000043</v>
+        <v>-11.030000000000001</v>
       </c>
       <c r="Q45">
         <f t="shared" si="5"/>
-        <v>-15.280000000000001</v>
+        <v>-17.61999999999999</v>
       </c>
       <c r="R45">
         <f t="shared" si="5"/>
-        <v>-13.370000000000005</v>
+        <v>-16.78</v>
       </c>
       <c r="S45">
         <f t="shared" si="5"/>
-        <v>-9.7199999999999989</v>
+        <v>-13.889999999999986</v>
       </c>
       <c r="T45">
         <f t="shared" si="5"/>
-        <v>-6.789999999999992</v>
+        <v>-10.939999999999998</v>
       </c>
       <c r="U45">
         <f t="shared" si="5"/>
-        <v>-6.5400000000000205</v>
+        <v>-10.25</v>
       </c>
       <c r="V45">
         <f t="shared" si="5"/>
-        <v>-10.599999999999994</v>
+        <v>-14.219999999999999</v>
       </c>
       <c r="W45">
         <f t="shared" si="5"/>
-        <v>-15.139999999999986</v>
+        <v>-18.699999999999989</v>
       </c>
       <c r="X45">
         <f t="shared" si="5"/>
-        <v>-15.650000000000006</v>
+        <v>-19.109999999999985</v>
       </c>
       <c r="Y45">
         <f t="shared" si="5"/>
-        <v>-14.299999999999983</v>
+        <v>-17.689999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
@@ -6351,47 +6741,47 @@
       </c>
       <c r="B46">
         <f t="shared" ref="B46:L46" si="6">B5-B26</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C46">
         <f t="shared" si="6"/>
-        <v>-19.499999999999986</v>
+        <v>-5.4499999999999886</v>
       </c>
       <c r="D46">
         <f t="shared" si="6"/>
-        <v>-19.25</v>
+        <v>-5.3199999999999932</v>
       </c>
       <c r="E46">
         <f t="shared" si="6"/>
-        <v>-18.590000000000003</v>
+        <v>-4.9000000000000057</v>
       </c>
       <c r="F46">
         <f t="shared" si="6"/>
-        <v>-18.909999999999997</v>
+        <v>-5.5</v>
       </c>
       <c r="G46">
         <f t="shared" si="6"/>
-        <v>-19.14</v>
+        <v>-6.0499999999999972</v>
       </c>
       <c r="H46">
         <f t="shared" si="6"/>
-        <v>-19.150000000000006</v>
+        <v>-6.3800000000000097</v>
       </c>
       <c r="I46">
         <f t="shared" si="6"/>
-        <v>-19.36</v>
+        <v>-6.75</v>
       </c>
       <c r="J46">
         <f t="shared" si="6"/>
-        <v>-19.539999999999992</v>
+        <v>-7.0099999999999909</v>
       </c>
       <c r="K46">
         <f t="shared" si="6"/>
-        <v>-19.36</v>
+        <v>-6.8799999999999955</v>
       </c>
       <c r="L46">
         <f t="shared" si="6"/>
-        <v>-19.820000000000007</v>
+        <v>-7.3900000000000006</v>
       </c>
       <c r="O46">
         <f t="shared" ref="O46:Y46" si="7">O5-O26</f>
@@ -6399,43 +6789,43 @@
       </c>
       <c r="P46">
         <f t="shared" si="7"/>
-        <v>-9.57</v>
+        <v>-11.009999999999998</v>
       </c>
       <c r="Q46">
         <f t="shared" si="7"/>
-        <v>-15.670000000000002</v>
+        <v>-17.930000000000007</v>
       </c>
       <c r="R46">
         <f t="shared" si="7"/>
-        <v>-13.789999999999992</v>
+        <v>-17</v>
       </c>
       <c r="S46">
         <f t="shared" si="7"/>
-        <v>-10.300000000000011</v>
+        <v>-14.29000000000002</v>
       </c>
       <c r="T46">
         <f t="shared" si="7"/>
-        <v>-7.3900000000000148</v>
+        <v>-11.319999999999993</v>
       </c>
       <c r="U46">
         <f t="shared" si="7"/>
-        <v>-6.6599999999999966</v>
+        <v>-10.159999999999997</v>
       </c>
       <c r="V46">
         <f t="shared" si="7"/>
-        <v>-10.650000000000006</v>
+        <v>-14.060000000000002</v>
       </c>
       <c r="W46">
         <f t="shared" si="7"/>
-        <v>-12.789999999999992</v>
+        <v>-16.169999999999987</v>
       </c>
       <c r="X46">
         <f t="shared" si="7"/>
-        <v>-14.599999999999994</v>
+        <v>-17.909999999999997</v>
       </c>
       <c r="Y46">
         <f t="shared" si="7"/>
-        <v>-13.549999999999983</v>
+        <v>-16.789999999999992</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
@@ -6444,47 +6834,47 @@
       </c>
       <c r="B47">
         <f t="shared" ref="B47:L47" si="8">B6-B27</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C47">
         <f t="shared" si="8"/>
-        <v>-19.410000000000011</v>
+        <v>-5.3200000000000216</v>
       </c>
       <c r="D47">
         <f t="shared" si="8"/>
-        <v>-18.840000000000003</v>
+        <v>-4.8100000000000165</v>
       </c>
       <c r="E47">
         <f t="shared" si="8"/>
-        <v>-18.480000000000004</v>
+        <v>-4.6200000000000045</v>
       </c>
       <c r="F47">
         <f t="shared" si="8"/>
-        <v>-18.689999999999998</v>
+        <v>-5.1099999999999994</v>
       </c>
       <c r="G47">
         <f t="shared" si="8"/>
-        <v>-19.339999999999989</v>
+        <v>-6.0499999999999972</v>
       </c>
       <c r="H47">
         <f t="shared" si="8"/>
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="I47">
         <f t="shared" si="8"/>
-        <v>-19.649999999999991</v>
+        <v>-6.7800000000000011</v>
       </c>
       <c r="J47">
         <f t="shared" si="8"/>
-        <v>-20.840000000000003</v>
+        <v>-8.039999999999992</v>
       </c>
       <c r="K47">
         <f t="shared" si="8"/>
-        <v>-21.089999999999989</v>
+        <v>-8.3499999999999943</v>
       </c>
       <c r="L47">
         <f t="shared" si="8"/>
-        <v>-20.950000000000003</v>
+        <v>-8.2600000000000051</v>
       </c>
       <c r="O47">
         <f t="shared" ref="O47:Y47" si="9">O6-O27</f>
@@ -6492,43 +6882,43 @@
       </c>
       <c r="P47">
         <f t="shared" si="9"/>
-        <v>-10.849999999999994</v>
+        <v>-12.239999999999995</v>
       </c>
       <c r="Q47">
         <f t="shared" si="9"/>
-        <v>-15.959999999999994</v>
+        <v>-18.129999999999995</v>
       </c>
       <c r="R47">
         <f t="shared" si="9"/>
-        <v>-14.710000000000008</v>
+        <v>-17.700000000000017</v>
       </c>
       <c r="S47">
         <f t="shared" si="9"/>
-        <v>-10.70999999999998</v>
+        <v>-14.509999999999991</v>
       </c>
       <c r="T47">
         <f t="shared" si="9"/>
-        <v>-8.1200000000000045</v>
+        <v>-11.879999999999995</v>
       </c>
       <c r="U47">
         <f t="shared" si="9"/>
-        <v>-7.0099999999999909</v>
+        <v>-10.370000000000005</v>
       </c>
       <c r="V47">
         <f t="shared" si="9"/>
-        <v>-9.1500000000000057</v>
+        <v>-12.430000000000007</v>
       </c>
       <c r="W47">
         <f t="shared" si="9"/>
-        <v>-11.439999999999998</v>
+        <v>-14.710000000000008</v>
       </c>
       <c r="X47">
         <f t="shared" si="9"/>
-        <v>-12.419999999999987</v>
+        <v>-15.620000000000005</v>
       </c>
       <c r="Y47">
         <f t="shared" si="9"/>
-        <v>-11.699999999999989</v>
+        <v>-14.829999999999984</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
@@ -6537,47 +6927,47 @@
       </c>
       <c r="B48">
         <f t="shared" ref="B48:L48" si="10">B7-B28</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C48">
         <f t="shared" si="10"/>
-        <v>-18.97999999999999</v>
+        <v>-4.8599999999999852</v>
       </c>
       <c r="D48">
         <f t="shared" si="10"/>
-        <v>-18.850000000000009</v>
+        <v>-4.75</v>
       </c>
       <c r="E48">
         <f t="shared" si="10"/>
-        <v>-18.549999999999997</v>
+        <v>-4.5600000000000023</v>
       </c>
       <c r="F48">
         <f t="shared" si="10"/>
-        <v>-18.64</v>
+        <v>-4.9099999999999966</v>
       </c>
       <c r="G48">
         <f t="shared" si="10"/>
-        <v>-19.269999999999996</v>
+        <v>-5.8400000000000034</v>
       </c>
       <c r="H48">
         <f t="shared" si="10"/>
-        <v>-19.560000000000002</v>
+        <v>-6.4200000000000017</v>
       </c>
       <c r="I48">
         <f t="shared" si="10"/>
-        <v>-19.489999999999995</v>
+        <v>-6.4699999999999989</v>
       </c>
       <c r="J48">
         <f t="shared" si="10"/>
-        <v>-21.450000000000003</v>
+        <v>-8.5</v>
       </c>
       <c r="K48">
         <f t="shared" si="10"/>
-        <v>-21.580000000000005</v>
+        <v>-8.6899999999999977</v>
       </c>
       <c r="L48">
         <f t="shared" si="10"/>
-        <v>-21.820000000000007</v>
+        <v>-9</v>
       </c>
       <c r="O48">
         <f t="shared" ref="O48:Y48" si="11">O7-O28</f>
@@ -6585,43 +6975,43 @@
       </c>
       <c r="P48">
         <f t="shared" si="11"/>
-        <v>-10.409999999999997</v>
+        <v>-11.759999999999998</v>
       </c>
       <c r="Q48">
         <f t="shared" si="11"/>
-        <v>-15.86</v>
+        <v>-17.939999999999998</v>
       </c>
       <c r="R48">
         <f t="shared" si="11"/>
-        <v>-15.239999999999995</v>
+        <v>-18.009999999999991</v>
       </c>
       <c r="S48">
         <f t="shared" si="11"/>
-        <v>-11.050000000000011</v>
+        <v>-14.629999999999995</v>
       </c>
       <c r="T48">
         <f t="shared" si="11"/>
-        <v>-8.3700000000000045</v>
+        <v>-12.010000000000019</v>
       </c>
       <c r="U48">
         <f t="shared" si="11"/>
-        <v>-7.9899999999999807</v>
+        <v>-11.22999999999999</v>
       </c>
       <c r="V48">
         <f t="shared" si="11"/>
-        <v>-7.7599999999999909</v>
+        <v>-10.939999999999998</v>
       </c>
       <c r="W48">
         <f t="shared" si="11"/>
-        <v>-10.269999999999982</v>
+        <v>-13.439999999999998</v>
       </c>
       <c r="X48">
         <f t="shared" si="11"/>
-        <v>-10.819999999999993</v>
+        <v>-13.939999999999998</v>
       </c>
       <c r="Y48">
         <f t="shared" si="11"/>
-        <v>-9.8899999999999864</v>
+        <v>-12.930000000000007</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
@@ -6630,47 +7020,47 @@
       </c>
       <c r="B49">
         <f t="shared" ref="B49:L49" si="12">B8-B29</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C49">
         <f t="shared" si="12"/>
-        <v>-19.050000000000011</v>
+        <v>-4.8900000000000006</v>
       </c>
       <c r="D49">
         <f t="shared" si="12"/>
-        <v>-18.53</v>
+        <v>-4.3599999999999994</v>
       </c>
       <c r="E49">
         <f t="shared" si="12"/>
-        <v>-18.759999999999991</v>
+        <v>-4.6799999999999926</v>
       </c>
       <c r="F49">
         <f t="shared" si="12"/>
-        <v>-18.659999999999997</v>
+        <v>-4.7900000000000063</v>
       </c>
       <c r="G49">
         <f t="shared" si="12"/>
-        <v>-19.36999999999999</v>
+        <v>-5.789999999999992</v>
       </c>
       <c r="H49">
         <f t="shared" si="12"/>
-        <v>-19.480000000000004</v>
+        <v>-6.210000000000008</v>
       </c>
       <c r="I49">
         <f t="shared" si="12"/>
-        <v>-19.829999999999998</v>
+        <v>-6.6899999999999977</v>
       </c>
       <c r="J49">
         <f t="shared" si="12"/>
-        <v>-20.899999999999991</v>
+        <v>-7.8199999999999932</v>
       </c>
       <c r="K49">
         <f t="shared" si="12"/>
-        <v>-22.410000000000004</v>
+        <v>-9.39</v>
       </c>
       <c r="L49">
         <f t="shared" si="12"/>
-        <v>-22.46</v>
+        <v>-9.509999999999998</v>
       </c>
       <c r="O49">
         <f t="shared" ref="O49:Y49" si="13">O8-O29</f>
@@ -6678,43 +7068,43 @@
       </c>
       <c r="P49">
         <f t="shared" si="13"/>
-        <v>-11.21</v>
+        <v>-12.5</v>
       </c>
       <c r="Q49">
         <f t="shared" si="13"/>
-        <v>-17.22</v>
+        <v>-19.189999999999998</v>
       </c>
       <c r="R49">
         <f t="shared" si="13"/>
-        <v>-17.039999999999992</v>
+        <v>-19.61999999999999</v>
       </c>
       <c r="S49">
         <f t="shared" si="13"/>
-        <v>-12.140000000000015</v>
+        <v>-15.439999999999998</v>
       </c>
       <c r="T49">
         <f t="shared" si="13"/>
-        <v>-9.039999999999992</v>
+        <v>-12.539999999999992</v>
       </c>
       <c r="U49">
         <f t="shared" si="13"/>
-        <v>-8.1999999999999886</v>
+        <v>-11.330000000000013</v>
       </c>
       <c r="V49">
         <f t="shared" si="13"/>
-        <v>-7.6899999999999977</v>
+        <v>-10.75</v>
       </c>
       <c r="W49">
         <f t="shared" si="13"/>
-        <v>-8.6999999999999886</v>
+        <v>-11.759999999999991</v>
       </c>
       <c r="X49">
         <f t="shared" si="13"/>
-        <v>-8.3799999999999955</v>
+        <v>-11.419999999999987</v>
       </c>
       <c r="Y49">
         <f t="shared" si="13"/>
-        <v>-9.3499999999999943</v>
+        <v>-12.299999999999983</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
@@ -6723,47 +7113,47 @@
       </c>
       <c r="B50">
         <f t="shared" ref="B50:L50" si="14">B9-B30</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C50">
         <f t="shared" si="14"/>
-        <v>-18.250000000000014</v>
+        <v>-4.0500000000000114</v>
       </c>
       <c r="D50">
         <f t="shared" si="14"/>
-        <v>-18.47</v>
+        <v>-4.2399999999999949</v>
       </c>
       <c r="E50">
         <f t="shared" si="14"/>
-        <v>-18.260000000000005</v>
+        <v>-4.0900000000000034</v>
       </c>
       <c r="F50">
         <f t="shared" si="14"/>
-        <v>-18.409999999999997</v>
+        <v>-4.3799999999999955</v>
       </c>
       <c r="G50">
         <f t="shared" si="14"/>
-        <v>-19.02000000000001</v>
+        <v>-5.2600000000000051</v>
       </c>
       <c r="H50">
         <f t="shared" si="14"/>
-        <v>-19.240000000000009</v>
+        <v>-5.8100000000000023</v>
       </c>
       <c r="I50">
         <f t="shared" si="14"/>
-        <v>-19.699999999999996</v>
+        <v>-6.4200000000000017</v>
       </c>
       <c r="J50">
         <f t="shared" si="14"/>
-        <v>-20.210000000000008</v>
+        <v>-7.0100000000000051</v>
       </c>
       <c r="K50">
         <f t="shared" si="14"/>
-        <v>-22.15</v>
+        <v>-9.009999999999998</v>
       </c>
       <c r="L50">
         <f t="shared" si="14"/>
-        <v>-23.39</v>
+        <v>-10.32</v>
       </c>
       <c r="O50">
         <f t="shared" ref="O50:Y50" si="15">O9-O30</f>
@@ -6771,43 +7161,43 @@
       </c>
       <c r="P50">
         <f t="shared" si="15"/>
-        <v>-10.699999999999996</v>
+        <v>-11.93</v>
       </c>
       <c r="Q50">
         <f t="shared" si="15"/>
-        <v>-16.909999999999997</v>
+        <v>-18.769999999999996</v>
       </c>
       <c r="R50">
         <f t="shared" si="15"/>
-        <v>-17.049999999999997</v>
+        <v>-19.450000000000003</v>
       </c>
       <c r="S50">
         <f t="shared" si="15"/>
-        <v>-13.159999999999997</v>
+        <v>-16.139999999999986</v>
       </c>
       <c r="T50">
         <f t="shared" si="15"/>
-        <v>-9.4800000000000182</v>
+        <v>-12.780000000000001</v>
       </c>
       <c r="U50">
         <f t="shared" si="15"/>
-        <v>-8.5699999999999932</v>
+        <v>-11.539999999999992</v>
       </c>
       <c r="V50">
         <f t="shared" si="15"/>
-        <v>-8.1400000000000148</v>
+        <v>-11.060000000000002</v>
       </c>
       <c r="W50">
         <f t="shared" si="15"/>
-        <v>-7.0099999999999909</v>
+        <v>-9.9499999999999886</v>
       </c>
       <c r="X50">
         <f t="shared" si="15"/>
-        <v>-7.8299999999999841</v>
+        <v>-10.769999999999982</v>
       </c>
       <c r="Y50">
         <f t="shared" si="15"/>
-        <v>-8.1800000000000068</v>
+        <v>-11.030000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
@@ -6816,47 +7206,47 @@
       </c>
       <c r="B51">
         <f t="shared" ref="B51:L51" si="16">B10-B31</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C51">
         <f t="shared" si="16"/>
-        <v>-18.39</v>
+        <v>-4.1700000000000017</v>
       </c>
       <c r="D51">
         <f t="shared" si="16"/>
-        <v>-18.120000000000005</v>
+        <v>-3.8300000000000125</v>
       </c>
       <c r="E51">
         <f t="shared" si="16"/>
-        <v>-17.52000000000001</v>
+        <v>-3.2700000000000102</v>
       </c>
       <c r="F51">
         <f t="shared" si="16"/>
-        <v>-17.939999999999998</v>
+        <v>-3.7800000000000011</v>
       </c>
       <c r="G51">
         <f t="shared" si="16"/>
-        <v>-18.670000000000002</v>
+        <v>-4.6899999999999977</v>
       </c>
       <c r="H51">
         <f t="shared" si="16"/>
-        <v>-19.179999999999993</v>
+        <v>-5.5499999999999972</v>
       </c>
       <c r="I51">
         <f t="shared" si="16"/>
-        <v>-19.409999999999997</v>
+        <v>-5.9399999999999977</v>
       </c>
       <c r="J51">
         <f t="shared" si="16"/>
-        <v>-19.889999999999993</v>
+        <v>-6.509999999999998</v>
       </c>
       <c r="K51">
         <f t="shared" si="16"/>
-        <v>-21.080000000000005</v>
+        <v>-7.75</v>
       </c>
       <c r="L51">
         <f t="shared" si="16"/>
-        <v>-22.75</v>
+        <v>-9.490000000000002</v>
       </c>
       <c r="O51">
         <f t="shared" ref="O51:Y51" si="17">O10-O31</f>
@@ -6864,43 +7254,43 @@
       </c>
       <c r="P51">
         <f t="shared" si="17"/>
-        <v>-11.36</v>
+        <v>-12.519999999999996</v>
       </c>
       <c r="Q51">
         <f t="shared" si="17"/>
-        <v>-16.879999999999995</v>
+        <v>-18.61999999999999</v>
       </c>
       <c r="R51">
         <f t="shared" si="17"/>
-        <v>-17.849999999999994</v>
+        <v>-20.069999999999993</v>
       </c>
       <c r="S51">
         <f t="shared" si="17"/>
-        <v>-14.969999999999999</v>
+        <v>-17.659999999999997</v>
       </c>
       <c r="T51">
         <f t="shared" si="17"/>
-        <v>-10.030000000000001</v>
+        <v>-13.030000000000001</v>
       </c>
       <c r="U51">
         <f t="shared" si="17"/>
-        <v>-8.3900000000000148</v>
+        <v>-11.130000000000024</v>
       </c>
       <c r="V51">
         <f t="shared" si="17"/>
-        <v>-8.1200000000000045</v>
+        <v>-10.829999999999984</v>
       </c>
       <c r="W51">
         <f t="shared" si="17"/>
-        <v>-7.4699999999999989</v>
+        <v>-10.20999999999998</v>
       </c>
       <c r="X51">
         <f t="shared" si="17"/>
-        <v>-6</v>
+        <v>-8.7600000000000193</v>
       </c>
       <c r="Y51">
         <f t="shared" si="17"/>
-        <v>-8.1400000000000148</v>
+        <v>-10.850000000000023</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
@@ -6909,47 +7299,47 @@
       </c>
       <c r="B52">
         <f t="shared" ref="B52:L52" si="18">B11-B32</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C52">
         <f t="shared" si="18"/>
-        <v>-17.810000000000002</v>
+        <v>-3.5499999999999972</v>
       </c>
       <c r="D52">
         <f t="shared" si="18"/>
-        <v>-16.850000000000009</v>
+        <v>-2.5</v>
       </c>
       <c r="E52">
         <f t="shared" si="18"/>
-        <v>-17.39</v>
+        <v>-3.0600000000000023</v>
       </c>
       <c r="F52">
         <f t="shared" si="18"/>
-        <v>-17.769999999999996</v>
+        <v>-3.4899999999999949</v>
       </c>
       <c r="G52">
         <f t="shared" si="18"/>
-        <v>-18.599999999999994</v>
+        <v>-4.4099999999999966</v>
       </c>
       <c r="H52">
         <f t="shared" si="18"/>
-        <v>-19.14</v>
+        <v>-5.230000000000004</v>
       </c>
       <c r="I52">
         <f t="shared" si="18"/>
-        <v>-19.290000000000006</v>
+        <v>-5.6000000000000085</v>
       </c>
       <c r="J52">
         <f t="shared" si="18"/>
-        <v>-19.82</v>
+        <v>-6.240000000000002</v>
       </c>
       <c r="K52">
         <f t="shared" si="18"/>
-        <v>-20.430000000000003</v>
+        <v>-6.93</v>
       </c>
       <c r="L52">
         <f t="shared" si="18"/>
-        <v>-21.619999999999997</v>
+        <v>-8.1999999999999957</v>
       </c>
       <c r="O52">
         <f t="shared" ref="O52:Y52" si="19">O11-O32</f>
@@ -6957,43 +7347,43 @@
       </c>
       <c r="P52">
         <f t="shared" si="19"/>
-        <v>-10.93</v>
+        <v>-12.020000000000003</v>
       </c>
       <c r="Q52">
         <f t="shared" si="19"/>
-        <v>-15.22999999999999</v>
+        <v>-16.849999999999994</v>
       </c>
       <c r="R52">
         <f t="shared" si="19"/>
-        <v>-18.079999999999998</v>
+        <v>-20.099999999999994</v>
       </c>
       <c r="S52">
         <f t="shared" si="19"/>
-        <v>-15.989999999999995</v>
+        <v>-18.399999999999991</v>
       </c>
       <c r="T52">
         <f t="shared" si="19"/>
-        <v>-11.899999999999977</v>
+        <v>-14.569999999999993</v>
       </c>
       <c r="U52">
         <f t="shared" si="19"/>
-        <v>-9.1200000000000045</v>
+        <v>-11.539999999999992</v>
       </c>
       <c r="V52">
         <f t="shared" si="19"/>
-        <v>-8.0300000000000011</v>
+        <v>-10.430000000000007</v>
       </c>
       <c r="W52">
         <f t="shared" si="19"/>
-        <v>-7.2399999999999807</v>
+        <v>-9.7199999999999989</v>
       </c>
       <c r="X52">
         <f t="shared" si="19"/>
-        <v>-6.3299999999999841</v>
+        <v>-8.8699999999999761</v>
       </c>
       <c r="Y52">
         <f t="shared" si="19"/>
-        <v>-4.6500000000000057</v>
+        <v>-7.2000000000000171</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
@@ -7002,47 +7392,47 @@
       </c>
       <c r="B53">
         <f t="shared" ref="B53:L53" si="20">B12-B33</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C53">
         <f t="shared" si="20"/>
-        <v>-17.320000000000007</v>
+        <v>-3.0500000000000114</v>
       </c>
       <c r="D53">
         <f t="shared" si="20"/>
-        <v>-17</v>
+        <v>-2.6099999999999994</v>
       </c>
       <c r="E53">
         <f t="shared" si="20"/>
-        <v>-17.11</v>
+        <v>-2.7099999999999937</v>
       </c>
       <c r="F53">
         <f t="shared" si="20"/>
-        <v>-17.89</v>
+        <v>-3.5</v>
       </c>
       <c r="G53">
         <f t="shared" si="20"/>
-        <v>-18.52000000000001</v>
+        <v>-4.1900000000000119</v>
       </c>
       <c r="H53">
         <f t="shared" si="20"/>
-        <v>-19.04</v>
+        <v>-4.8800000000000026</v>
       </c>
       <c r="I53">
         <f t="shared" si="20"/>
-        <v>-19.29</v>
+        <v>-5.3399999999999963</v>
       </c>
       <c r="J53">
         <f t="shared" si="20"/>
-        <v>-19.759999999999998</v>
+        <v>-5.9499999999999957</v>
       </c>
       <c r="K53">
         <f t="shared" si="20"/>
-        <v>-20.47</v>
+        <v>-6.7799999999999976</v>
       </c>
       <c r="L53">
         <f t="shared" si="20"/>
-        <v>-21.2</v>
+        <v>-7.629999999999999</v>
       </c>
       <c r="O53">
         <f t="shared" ref="O53:Y53" si="21">O12-O33</f>
@@ -7050,43 +7440,43 @@
       </c>
       <c r="P53">
         <f t="shared" si="21"/>
-        <v>-10.690000000000001</v>
+        <v>-11.690000000000001</v>
       </c>
       <c r="Q53">
         <f t="shared" si="21"/>
-        <v>-15.799999999999997</v>
+        <v>-17.299999999999997</v>
       </c>
       <c r="R53">
         <f t="shared" si="21"/>
-        <v>-18.209999999999994</v>
+        <v>-20.049999999999997</v>
       </c>
       <c r="S53">
         <f t="shared" si="21"/>
-        <v>-16.480000000000004</v>
+        <v>-18.64</v>
       </c>
       <c r="T53">
         <f t="shared" si="21"/>
-        <v>-12.95999999999998</v>
+        <v>-15.379999999999995</v>
       </c>
       <c r="U53">
         <f t="shared" si="21"/>
-        <v>-10.230000000000018</v>
+        <v>-12.5</v>
       </c>
       <c r="V53">
         <f t="shared" si="21"/>
-        <v>-8.9699999999999989</v>
+        <v>-10.949999999999989</v>
       </c>
       <c r="W53">
         <f t="shared" si="21"/>
-        <v>-7.7800000000000011</v>
+        <v>-9.8299999999999841</v>
       </c>
       <c r="X53">
         <f t="shared" si="21"/>
-        <v>-6.460000000000008</v>
+        <v>-8.6500000000000057</v>
       </c>
       <c r="Y53">
         <f t="shared" si="21"/>
-        <v>-4.9199999999999875</v>
+        <v>-7.1899999999999977</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
@@ -7095,47 +7485,47 @@
       </c>
       <c r="B54">
         <f t="shared" ref="B54:L54" si="22">B13-B34</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C54">
         <f t="shared" si="22"/>
-        <v>-17.25</v>
+        <v>-2.9599999999999937</v>
       </c>
       <c r="D54">
         <f t="shared" si="22"/>
-        <v>-16.439999999999998</v>
+        <v>-2</v>
       </c>
       <c r="E54">
         <f t="shared" si="22"/>
-        <v>-16.800000000000011</v>
+        <v>-2.3200000000000074</v>
       </c>
       <c r="F54">
         <f t="shared" si="22"/>
-        <v>-17.009999999999991</v>
+        <v>-2.539999999999992</v>
       </c>
       <c r="G54">
         <f t="shared" si="22"/>
-        <v>-17.699999999999996</v>
+        <v>-3.269999999999996</v>
       </c>
       <c r="H54">
         <f t="shared" si="22"/>
-        <v>-18.78</v>
+        <v>-4.43</v>
       </c>
       <c r="I54">
         <f t="shared" si="22"/>
-        <v>-19.650000000000002</v>
+        <v>-5.5</v>
       </c>
       <c r="J54">
         <f t="shared" si="22"/>
-        <v>-19.849999999999998</v>
+        <v>-5.7899999999999991</v>
       </c>
       <c r="K54">
         <f t="shared" si="22"/>
-        <v>-20.310000000000002</v>
+        <v>-6.3299999999999983</v>
       </c>
       <c r="L54">
         <f t="shared" si="22"/>
-        <v>-21.27</v>
+        <v>-7.4399999999999995</v>
       </c>
       <c r="O54">
         <f t="shared" ref="O54:Y54" si="23">O13-O34</f>
@@ -7143,43 +7533,43 @@
       </c>
       <c r="P54">
         <f t="shared" si="23"/>
-        <v>-9.5500000000000043</v>
+        <v>-10.450000000000003</v>
       </c>
       <c r="Q54">
         <f t="shared" si="23"/>
-        <v>-15.569999999999993</v>
+        <v>-16.949999999999996</v>
       </c>
       <c r="R54">
         <f t="shared" si="23"/>
-        <v>-17.190000000000012</v>
+        <v>-18.840000000000003</v>
       </c>
       <c r="S54">
         <f t="shared" si="23"/>
-        <v>-17.269999999999996</v>
+        <v>-19.179999999999993</v>
       </c>
       <c r="T54">
         <f t="shared" si="23"/>
-        <v>-14.920000000000002</v>
+        <v>-17.070000000000007</v>
       </c>
       <c r="U54">
         <f t="shared" si="23"/>
-        <v>-11.460000000000008</v>
+        <v>-13.630000000000024</v>
       </c>
       <c r="V54">
         <f t="shared" si="23"/>
-        <v>-10.150000000000006</v>
+        <v>-11.900000000000006</v>
       </c>
       <c r="W54">
         <f t="shared" si="23"/>
-        <v>-8.3499999999999943</v>
+        <v>-9.9599999999999795</v>
       </c>
       <c r="X54">
         <f t="shared" si="23"/>
-        <v>-7.3799999999999955</v>
+        <v>-9</v>
       </c>
       <c r="Y54">
         <f t="shared" si="23"/>
-        <v>-6.210000000000008</v>
+        <v>-7.8900000000000148</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
@@ -7188,47 +7578,47 @@
       </c>
       <c r="B55">
         <f t="shared" ref="B55:L55" si="24">B14-B35</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C55">
         <f t="shared" si="24"/>
-        <v>-16.919999999999987</v>
+        <v>-2.6199999999999903</v>
       </c>
       <c r="D55">
         <f t="shared" si="24"/>
-        <v>-16.180000000000007</v>
+        <v>-1.7000000000000028</v>
       </c>
       <c r="E55">
         <f t="shared" si="24"/>
-        <v>-15.88000000000001</v>
+        <v>-1.3599999999999994</v>
       </c>
       <c r="F55">
         <f t="shared" si="24"/>
-        <v>-16.169999999999995</v>
+        <v>-1.6400000000000006</v>
       </c>
       <c r="G55">
         <f t="shared" si="24"/>
-        <v>-17.179999999999993</v>
+        <v>-2.6699999999999875</v>
       </c>
       <c r="H55">
         <f t="shared" si="24"/>
-        <v>-18.379999999999995</v>
+        <v>-3.8999999999999986</v>
       </c>
       <c r="I55">
         <f t="shared" si="24"/>
-        <v>-19.28</v>
+        <v>-4.9200000000000017</v>
       </c>
       <c r="J55">
         <f t="shared" si="24"/>
-        <v>-19.91</v>
+        <v>-5.6700000000000017</v>
       </c>
       <c r="K55">
         <f t="shared" si="24"/>
-        <v>-20.610000000000003</v>
+        <v>-6.4600000000000009</v>
       </c>
       <c r="L55">
         <f t="shared" si="24"/>
-        <v>-21.16</v>
+        <v>-7.1099999999999994</v>
       </c>
       <c r="O55">
         <f t="shared" ref="O55:Y55" si="25">O14-O35</f>
@@ -7236,43 +7626,43 @@
       </c>
       <c r="P55">
         <f t="shared" si="25"/>
-        <v>-9.68</v>
+        <v>-10.469999999999999</v>
       </c>
       <c r="Q55">
         <f t="shared" si="25"/>
-        <v>-13.910000000000004</v>
+        <v>-15.160000000000004</v>
       </c>
       <c r="R55">
         <f t="shared" si="25"/>
-        <v>-17.159999999999997</v>
+        <v>-18.649999999999991</v>
       </c>
       <c r="S55">
         <f t="shared" si="25"/>
-        <v>-17.569999999999993</v>
+        <v>-19.259999999999991</v>
       </c>
       <c r="T55">
         <f t="shared" si="25"/>
-        <v>-16.259999999999991</v>
+        <v>-18.14</v>
       </c>
       <c r="U55">
         <f t="shared" si="25"/>
-        <v>-13.200000000000003</v>
+        <v>-15.189999999999998</v>
       </c>
       <c r="V55">
         <f t="shared" si="25"/>
-        <v>-10.569999999999993</v>
+        <v>-12.329999999999984</v>
       </c>
       <c r="W55">
         <f t="shared" si="25"/>
-        <v>-9.2700000000000102</v>
+        <v>-10.689999999999998</v>
       </c>
       <c r="X55">
         <f t="shared" si="25"/>
-        <v>-8.6800000000000068</v>
+        <v>-9.9699999999999989</v>
       </c>
       <c r="Y55">
         <f t="shared" si="25"/>
-        <v>-8.1399999999999864</v>
+        <v>-9.3700000000000045</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
@@ -7281,47 +7671,47 @@
       </c>
       <c r="B56">
         <f t="shared" ref="B56:L56" si="26">B15-B36</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C56">
         <f t="shared" si="26"/>
-        <v>-16.259999999999991</v>
+        <v>-1.9599999999999937</v>
       </c>
       <c r="D56">
         <f t="shared" si="26"/>
-        <v>-15.950000000000003</v>
+        <v>-1.4399999999999977</v>
       </c>
       <c r="E56">
         <f t="shared" si="26"/>
-        <v>-16.019999999999996</v>
+        <v>-1.460000000000008</v>
       </c>
       <c r="F56">
         <f t="shared" si="26"/>
-        <v>-16.04</v>
+        <v>-1.4699999999999989</v>
       </c>
       <c r="G56">
         <f t="shared" si="26"/>
-        <v>-16.920000000000002</v>
+        <v>-2.3400000000000034</v>
       </c>
       <c r="H56">
         <f t="shared" si="26"/>
-        <v>-17.759999999999998</v>
+        <v>-3.1899999999999977</v>
       </c>
       <c r="I56">
         <f t="shared" si="26"/>
-        <v>-18.52</v>
+        <v>-4</v>
       </c>
       <c r="J56">
         <f t="shared" si="26"/>
-        <v>-19.54</v>
+        <v>-5.1400000000000006</v>
       </c>
       <c r="K56">
         <f t="shared" si="26"/>
-        <v>-20.09</v>
+        <v>-5.8100000000000005</v>
       </c>
       <c r="L56">
         <f t="shared" si="26"/>
-        <v>-20.740000000000002</v>
+        <v>-6.56</v>
       </c>
       <c r="O56">
         <f t="shared" ref="O56:Y56" si="27">O15-O36</f>
@@ -7329,43 +7719,43 @@
       </c>
       <c r="P56">
         <f t="shared" si="27"/>
-        <v>-9.4200000000000017</v>
+        <v>-10.080000000000002</v>
       </c>
       <c r="Q56">
         <f t="shared" si="27"/>
-        <v>-13.349999999999994</v>
+        <v>-14.46</v>
       </c>
       <c r="R56">
         <f t="shared" si="27"/>
-        <v>-16.669999999999995</v>
+        <v>-18</v>
       </c>
       <c r="S56">
         <f t="shared" si="27"/>
-        <v>-17.310000000000002</v>
+        <v>-18.799999999999997</v>
       </c>
       <c r="T56">
         <f t="shared" si="27"/>
-        <v>-16.299999999999997</v>
+        <v>-17.930000000000007</v>
       </c>
       <c r="U56">
         <f t="shared" si="27"/>
-        <v>-13.810000000000002</v>
+        <v>-15.560000000000002</v>
       </c>
       <c r="V56">
         <f t="shared" si="27"/>
-        <v>-11.149999999999991</v>
+        <v>-12.889999999999986</v>
       </c>
       <c r="W56">
         <f t="shared" si="27"/>
-        <v>-9.5999999999999943</v>
+        <v>-11</v>
       </c>
       <c r="X56">
         <f t="shared" si="27"/>
-        <v>-8.7699999999999818</v>
+        <v>-9.9199999999999875</v>
       </c>
       <c r="Y56">
         <f t="shared" si="27"/>
-        <v>-8.1299999999999955</v>
+        <v>-9.1500000000000057</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
@@ -7374,47 +7764,47 @@
       </c>
       <c r="B57">
         <f t="shared" ref="B57:L57" si="28">B16-B37</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C57">
         <f t="shared" si="28"/>
-        <v>-16.28</v>
+        <v>-1.9700000000000131</v>
       </c>
       <c r="D57">
         <f t="shared" si="28"/>
-        <v>-16</v>
+        <v>-1.4599999999999937</v>
       </c>
       <c r="E57">
         <f t="shared" si="28"/>
-        <v>-15.740000000000009</v>
+        <v>-1.1500000000000057</v>
       </c>
       <c r="F57">
         <f t="shared" si="28"/>
-        <v>-15.340000000000003</v>
+        <v>-0.73000000000000398</v>
       </c>
       <c r="G57">
         <f t="shared" si="28"/>
-        <v>-16</v>
+        <v>-1.3900000000000006</v>
       </c>
       <c r="H57">
         <f t="shared" si="28"/>
-        <v>-16.759999999999998</v>
+        <v>-2.1499999999999986</v>
       </c>
       <c r="I57">
         <f t="shared" si="28"/>
-        <v>-17.64</v>
+        <v>-3.0300000000000011</v>
       </c>
       <c r="J57">
         <f t="shared" si="28"/>
-        <v>-18.559999999999999</v>
+        <v>-4.009999999999998</v>
       </c>
       <c r="K57">
         <f t="shared" si="28"/>
-        <v>-19.37</v>
+        <v>-4.97</v>
       </c>
       <c r="L57">
         <f t="shared" si="28"/>
-        <v>-19.93</v>
+        <v>-5.6499999999999995</v>
       </c>
       <c r="O57">
         <f t="shared" ref="O57:Y57" si="29">O16-O37</f>
@@ -7422,43 +7812,43 @@
       </c>
       <c r="P57">
         <f t="shared" si="29"/>
-        <v>-9.2199999999999989</v>
+        <v>-9.75</v>
       </c>
       <c r="Q57">
         <f t="shared" si="29"/>
-        <v>-12.510000000000005</v>
+        <v>-13.470000000000002</v>
       </c>
       <c r="R57">
         <f t="shared" si="29"/>
-        <v>-13.940000000000005</v>
+        <v>-15.090000000000003</v>
       </c>
       <c r="S57">
         <f t="shared" si="29"/>
-        <v>-15.739999999999995</v>
+        <v>-17.029999999999994</v>
       </c>
       <c r="T57">
         <f t="shared" si="29"/>
-        <v>-15.660000000000011</v>
+        <v>-17.080000000000013</v>
       </c>
       <c r="U57">
         <f t="shared" si="29"/>
-        <v>-14.240000000000009</v>
+        <v>-15.760000000000005</v>
       </c>
       <c r="V57">
         <f t="shared" si="29"/>
-        <v>-11.819999999999993</v>
+        <v>-13.399999999999991</v>
       </c>
       <c r="W57">
         <f t="shared" si="29"/>
-        <v>-9.7900000000000063</v>
+        <v>-11.299999999999997</v>
       </c>
       <c r="X57">
         <f t="shared" si="29"/>
-        <v>-7.9899999999999949</v>
+        <v>-9.1700000000000017</v>
       </c>
       <c r="Y57">
         <f t="shared" si="29"/>
-        <v>-6.5300000000000011</v>
+        <v>-7.519999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
@@ -7467,47 +7857,47 @@
       </c>
       <c r="B58">
         <f t="shared" ref="B58:L58" si="30">B17-B38</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C58">
         <f t="shared" si="30"/>
-        <v>-15.490000000000009</v>
+        <v>-1.1800000000000068</v>
       </c>
       <c r="D58">
         <f t="shared" si="30"/>
-        <v>-15.409999999999997</v>
+        <v>-0.85000000000000853</v>
       </c>
       <c r="E58">
         <f t="shared" si="30"/>
-        <v>-15.14</v>
+        <v>-0.53000000000000114</v>
       </c>
       <c r="F58">
         <f t="shared" si="30"/>
-        <v>-14.689999999999998</v>
+        <v>-4.9999999999997158E-2</v>
       </c>
       <c r="G58">
         <f t="shared" si="30"/>
-        <v>-14.869999999999997</v>
+        <v>-0.22999999999999687</v>
       </c>
       <c r="H58">
         <f t="shared" si="30"/>
-        <v>-15.469999999999999</v>
+        <v>-0.82000000000000028</v>
       </c>
       <c r="I58">
         <f t="shared" si="30"/>
-        <v>-15.850000000000001</v>
+        <v>-1.1999999999999993</v>
       </c>
       <c r="J58">
         <f t="shared" si="30"/>
-        <v>-16.97</v>
+        <v>-2.33</v>
       </c>
       <c r="K58">
         <f t="shared" si="30"/>
-        <v>-18.21</v>
+        <v>-3.6599999999999997</v>
       </c>
       <c r="L58">
         <f t="shared" si="30"/>
-        <v>-18.97</v>
+        <v>-4.57</v>
       </c>
       <c r="O58">
         <f t="shared" ref="O58:Y58" si="31">O17-O38</f>
@@ -7515,43 +7905,43 @@
       </c>
       <c r="P58">
         <f t="shared" si="31"/>
-        <v>-8.4000000000000021</v>
+        <v>-8.7900000000000009</v>
       </c>
       <c r="Q58">
         <f t="shared" si="31"/>
-        <v>-10.450000000000003</v>
+        <v>-11.260000000000002</v>
       </c>
       <c r="R58">
         <f t="shared" si="31"/>
-        <v>-12.709999999999994</v>
+        <v>-13.669999999999995</v>
       </c>
       <c r="S58">
         <f t="shared" si="31"/>
-        <v>-13.729999999999997</v>
+        <v>-14.810000000000002</v>
       </c>
       <c r="T58">
         <f t="shared" si="31"/>
-        <v>-13.740000000000009</v>
+        <v>-14.920000000000009</v>
       </c>
       <c r="U58">
         <f t="shared" si="31"/>
-        <v>-12.540000000000006</v>
+        <v>-13.810000000000002</v>
       </c>
       <c r="V58">
         <f t="shared" si="31"/>
-        <v>-11.420000000000002</v>
+        <v>-12.760000000000005</v>
       </c>
       <c r="W58">
         <f t="shared" si="31"/>
-        <v>-9.2600000000000051</v>
+        <v>-10.64</v>
       </c>
       <c r="X58">
         <f t="shared" si="31"/>
-        <v>-6.8400000000000034</v>
+        <v>-8.1500000000000057</v>
       </c>
       <c r="Y58">
         <f t="shared" si="31"/>
-        <v>-5.4299999999999926</v>
+        <v>-6.480000000000004</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.3">
@@ -7560,47 +7950,47 @@
       </c>
       <c r="B59">
         <f t="shared" ref="B59:L59" si="32">B18-B39</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C59">
         <f t="shared" si="32"/>
-        <v>-15.549999999999997</v>
+        <v>-1.2399999999999949</v>
       </c>
       <c r="D59">
         <f t="shared" si="32"/>
-        <v>-15.080000000000013</v>
+        <v>-0.52000000000001023</v>
       </c>
       <c r="E59">
         <f t="shared" si="32"/>
-        <v>-15.13000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="F59">
         <f t="shared" si="32"/>
-        <v>-14.770000000000003</v>
+        <v>-0.10999999999999943</v>
       </c>
       <c r="G59">
         <f t="shared" si="32"/>
-        <v>-13.830000000000005</v>
+        <v>0.83999999999999631</v>
       </c>
       <c r="H59">
         <f t="shared" si="32"/>
-        <v>-14.320000000000004</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="I59">
         <f t="shared" si="32"/>
-        <v>-14.97</v>
+        <v>-0.28000000000000114</v>
       </c>
       <c r="J59">
         <f t="shared" si="32"/>
-        <v>-15.52</v>
+        <v>-0.83000000000000007</v>
       </c>
       <c r="K59">
         <f t="shared" si="32"/>
-        <v>-16.850000000000001</v>
+        <v>-2.21</v>
       </c>
       <c r="L59">
         <f t="shared" si="32"/>
-        <v>-17.919999999999998</v>
+        <v>-3.389999999999997</v>
       </c>
       <c r="O59">
         <f t="shared" ref="O59:Y59" si="33">O18-O39</f>
@@ -7608,43 +7998,43 @@
       </c>
       <c r="P59">
         <f t="shared" si="33"/>
-        <v>-7.52</v>
+        <v>-7.79</v>
       </c>
       <c r="Q59">
         <f t="shared" si="33"/>
-        <v>-9.0500000000000007</v>
+        <v>-9.64</v>
       </c>
       <c r="R59">
         <f t="shared" si="33"/>
-        <v>-10.46</v>
+        <v>-11.220000000000002</v>
       </c>
       <c r="S59">
         <f t="shared" si="33"/>
-        <v>-11.240000000000002</v>
+        <v>-12.080000000000002</v>
       </c>
       <c r="T59">
         <f t="shared" si="33"/>
-        <v>-11.560000000000002</v>
+        <v>-12.470000000000006</v>
       </c>
       <c r="U59">
         <f t="shared" si="33"/>
-        <v>-11.160000000000004</v>
+        <v>-12.11</v>
       </c>
       <c r="V59">
         <f t="shared" si="33"/>
-        <v>-9.8699999999999974</v>
+        <v>-10.879999999999995</v>
       </c>
       <c r="W59">
         <f t="shared" si="33"/>
-        <v>-8.6900000000000048</v>
+        <v>-9.740000000000002</v>
       </c>
       <c r="X59">
         <f t="shared" si="33"/>
-        <v>-7.0300000000000011</v>
+        <v>-8.0799999999999983</v>
       </c>
       <c r="Y59">
         <f t="shared" si="33"/>
-        <v>-5.0799999999999983</v>
+        <v>-6.1099999999999994</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.3">
@@ -7653,47 +8043,47 @@
       </c>
       <c r="B60">
         <f t="shared" ref="B60:L60" si="34">B19-B40</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C60">
         <f t="shared" si="34"/>
-        <v>-15.030000000000001</v>
+        <v>-0.71999999999999886</v>
       </c>
       <c r="D60">
         <f t="shared" si="34"/>
-        <v>-14.490000000000009</v>
+        <v>6.9999999999993179E-2</v>
       </c>
       <c r="E60">
         <f t="shared" si="34"/>
-        <v>-14.329999999999998</v>
+        <v>0.31000000000000227</v>
       </c>
       <c r="F60">
         <f t="shared" si="34"/>
-        <v>-13.809999999999995</v>
+        <v>0.87000000000000455</v>
       </c>
       <c r="G60">
         <f t="shared" si="34"/>
-        <v>-13.560000000000002</v>
+        <v>1.1400000000000006</v>
       </c>
       <c r="H60">
         <f t="shared" si="34"/>
-        <v>-13.870000000000001</v>
+        <v>0.84999999999999432</v>
       </c>
       <c r="I60">
         <f t="shared" si="34"/>
-        <v>-14.3</v>
+        <v>0.42999999999999972</v>
       </c>
       <c r="J60">
         <f t="shared" si="34"/>
-        <v>-14.850000000000001</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="K60">
         <f t="shared" si="34"/>
-        <v>-15.69</v>
+        <v>-0.97000000000000064</v>
       </c>
       <c r="L60">
         <f t="shared" si="34"/>
-        <v>-16.899999999999999</v>
+        <v>-2.3099999999999987</v>
       </c>
       <c r="O60">
         <f t="shared" ref="O60:Y60" si="35">O19-O40</f>
@@ -7701,43 +8091,43 @@
       </c>
       <c r="P60">
         <f t="shared" si="35"/>
-        <v>-6.629999999999999</v>
+        <v>-6.76</v>
       </c>
       <c r="Q60">
         <f t="shared" si="35"/>
-        <v>-7.9799999999999995</v>
+        <v>-8.2799999999999994</v>
       </c>
       <c r="R60">
         <f t="shared" si="35"/>
-        <v>-8.35</v>
+        <v>-8.7999999999999989</v>
       </c>
       <c r="S60">
         <f t="shared" si="35"/>
-        <v>-8.5499999999999989</v>
+        <v>-9.0699999999999985</v>
       </c>
       <c r="T60">
         <f t="shared" si="35"/>
-        <v>-8.5399999999999991</v>
+        <v>-9.0799999999999983</v>
       </c>
       <c r="U60">
         <f t="shared" si="35"/>
-        <v>-9.0399999999999991</v>
+        <v>-9.5800000000000018</v>
       </c>
       <c r="V60">
         <f t="shared" si="35"/>
-        <v>-8.5399999999999991</v>
+        <v>-9.0799999999999983</v>
       </c>
       <c r="W60">
         <f t="shared" si="35"/>
-        <v>-7.75</v>
+        <v>-8.27</v>
       </c>
       <c r="X60">
         <f t="shared" si="35"/>
-        <v>-6.6400000000000006</v>
+        <v>-7.1400000000000006</v>
       </c>
       <c r="Y60">
         <f t="shared" si="35"/>
-        <v>-6.3500000000000014</v>
+        <v>-6.8299999999999983</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.3">
@@ -7746,47 +8136,47 @@
       </c>
       <c r="B61">
         <f t="shared" ref="B61:L61" si="36">B20-B41</f>
-        <v>-14.050000000000011</v>
+        <v>-0.17000000000001592</v>
       </c>
       <c r="C61">
         <f t="shared" si="36"/>
-        <v>-14.370000000000005</v>
+        <v>-6.0000000000002274E-2</v>
       </c>
       <c r="D61">
         <f t="shared" si="36"/>
-        <v>-13.989999999999995</v>
+        <v>0.57000000000000739</v>
       </c>
       <c r="E61">
         <f t="shared" si="36"/>
-        <v>-13.819999999999993</v>
+        <v>0.82999999999999829</v>
       </c>
       <c r="F61">
         <f t="shared" si="36"/>
-        <v>-13.550000000000004</v>
+        <v>1.1400000000000006</v>
       </c>
       <c r="G61">
         <f t="shared" si="36"/>
-        <v>-12.980000000000004</v>
+        <v>1.75</v>
       </c>
       <c r="H61">
         <f t="shared" si="36"/>
-        <v>-13.010000000000002</v>
+        <v>1.7399999999999949</v>
       </c>
       <c r="I61">
         <f t="shared" si="36"/>
-        <v>-13.57</v>
+        <v>1.2100000000000009</v>
       </c>
       <c r="J61">
         <f t="shared" si="36"/>
-        <v>-14.31</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="K61">
         <f t="shared" si="36"/>
-        <v>-15.110000000000001</v>
+        <v>-0.34999999999999964</v>
       </c>
       <c r="L61">
         <f t="shared" si="36"/>
-        <v>-16.37</v>
+        <v>-1.7700000000000031</v>
       </c>
       <c r="O61">
         <f t="shared" ref="O61:Y61" si="37">O20-O41</f>
@@ -7802,19 +8192,19 @@
       </c>
       <c r="R61">
         <f t="shared" si="37"/>
-        <v>-6.5299999999999994</v>
+        <v>-6.54</v>
       </c>
       <c r="S61">
         <f t="shared" si="37"/>
-        <v>-6.17</v>
+        <v>-6.1800000000000006</v>
       </c>
       <c r="T61">
         <f t="shared" si="37"/>
-        <v>-6.39</v>
+        <v>-6.4</v>
       </c>
       <c r="U61">
         <f t="shared" si="37"/>
-        <v>-6.25</v>
+        <v>-6.2600000000000007</v>
       </c>
       <c r="V61">
         <f t="shared" si="37"/>
@@ -7822,15 +8212,15 @@
       </c>
       <c r="W61">
         <f t="shared" si="37"/>
-        <v>-6.3000000000000007</v>
+        <v>-6.29</v>
       </c>
       <c r="X61">
         <f t="shared" si="37"/>
-        <v>-6.2600000000000007</v>
+        <v>-6.25</v>
       </c>
       <c r="Y61">
         <f t="shared" si="37"/>
-        <v>-6.49</v>
+        <v>-6.4799999999999995</v>
       </c>
     </row>
   </sheetData>
